--- a/BVSimulationFiles/103.xlsx
+++ b/BVSimulationFiles/103.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cbnor\Documents\Full Body Flow Model Project\BVSimulationFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\PHSAhome2.phsabc.ehcnet.ca\Cassidy.Northway\Remote Git\BVSimulationFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92ECB7E-25DA-462C-8A82-2E81024E9CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E3934C2-3746-4417-8886-6015040A64B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-4770" windowWidth="18240" windowHeight="28440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="plot-data (6)" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="plot-data (5)" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -389,10 +388,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U78"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B1">
@@ -461,5402 +456,5004 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>3.2645236028644432E-8</v>
+        <v>0.42695767682410668</v>
       </c>
       <c r="C2">
-        <v>3.292145203913488E-8</v>
+        <v>0.43057022678506102</v>
       </c>
       <c r="D2">
-        <v>3.3200005152790527E-8</v>
+        <v>0.43421334304784998</v>
       </c>
       <c r="E2">
-        <v>3.348091514417548E-8</v>
+        <v>0.4378872842383244</v>
       </c>
       <c r="F2">
-        <v>3.3764201955169241E-8</v>
+        <v>0.44159231117060571</v>
       </c>
       <c r="G2">
-        <v>3.4049885696382417E-8</v>
+        <v>0.44532868686560062</v>
       </c>
       <c r="H2">
-        <v>3.4337986648584399E-8</v>
+        <v>0.44909667656967373</v>
       </c>
       <c r="I2">
-        <v>3.4628525264143012E-8</v>
+        <v>0.45289654777347649</v>
       </c>
       <c r="J2">
-        <v>3.4921522168476488E-8</v>
+        <v>0.4567285702309376</v>
       </c>
       <c r="K2">
-        <v>3.5216998161517758E-8</v>
+        <v>0.46059301597841212</v>
       </c>
       <c r="L2">
-        <v>3.5514974219190887E-8</v>
+        <v>0.46449015935399351</v>
       </c>
       <c r="M2">
-        <v>3.581547149490023E-8</v>
+        <v>0.46842027701698902</v>
       </c>
       <c r="N2">
-        <v>3.6118511321032138E-8</v>
+        <v>0.47238364796755999</v>
       </c>
       <c r="O2">
-        <v>3.6424115210469353E-8</v>
+        <v>0.47638055356652809</v>
       </c>
       <c r="P2">
-        <v>3.6732304858118179E-8</v>
+        <v>0.48041127755534918</v>
       </c>
       <c r="Q2">
-        <v>3.704310214244859E-8</v>
+        <v>0.48447610607625552</v>
       </c>
       <c r="R2">
-        <v>3.7356529127047478E-8</v>
+        <v>0.48857532769257062</v>
       </c>
       <c r="S2">
-        <v>3.7672608062184887E-8</v>
+        <v>0.49270923340919309</v>
       </c>
       <c r="T2">
-        <v>3.7991361386393552E-8</v>
+        <v>0.49687811669325582</v>
       </c>
       <c r="U2">
-        <v>3.8312811728061872E-8</v>
+        <v>0.5010822734949586</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>1.2058080993402749E-2</v>
+        <v>1.701781970649904E-2</v>
       </c>
       <c r="B3">
-        <v>3.2916168885796718E-8</v>
+        <v>0.42845053583398129</v>
       </c>
       <c r="C3">
-        <v>3.3194677297936448E-8</v>
+        <v>0.43207571708850551</v>
       </c>
       <c r="D3">
-        <v>3.347554220957957E-8</v>
+        <v>0.43573157152004538</v>
       </c>
       <c r="E3">
-        <v>3.3758783559405359E-8</v>
+        <v>0.4394183586587383</v>
       </c>
       <c r="F3">
-        <v>3.4044421454797118E-8</v>
+        <v>0.44313634023064291</v>
       </c>
       <c r="G3">
-        <v>3.4332476173269621E-8</v>
+        <v>0.44688578017631969</v>
       </c>
       <c r="H3">
-        <v>3.4622968163908573E-8</v>
+        <v>0.4506669446695678</v>
       </c>
       <c r="I3">
-        <v>3.4915918048822278E-8</v>
+        <v>0.45448010213632101</v>
       </c>
       <c r="J3">
-        <v>3.5211346624605729E-8</v>
+        <v>0.45832552327370341</v>
       </c>
       <c r="K3">
-        <v>3.5509274863816831E-8</v>
+        <v>0.46220348106924591</v>
       </c>
       <c r="L3">
-        <v>3.5809723916465319E-8</v>
+        <v>0.46611425082026642</v>
       </c>
       <c r="M3">
-        <v>3.6112715111514163E-8</v>
+        <v>0.47005811015341231</v>
       </c>
       <c r="N3">
-        <v>3.6418269958393737E-8</v>
+        <v>0.47403533904436979</v>
       </c>
       <c r="O3">
-        <v>3.6726410148528848E-8</v>
+        <v>0.47804621983773993</v>
       </c>
       <c r="P3">
-        <v>3.7037157556878472E-8</v>
+        <v>0.4820910372670813</v>
       </c>
       <c r="Q3">
-        <v>3.7350534243488731E-8</v>
+        <v>0.48617007847512372</v>
       </c>
       <c r="R3">
-        <v>3.7666562455059049E-8</v>
+        <v>0.49028363303415318</v>
       </c>
       <c r="S3">
-        <v>3.7985264626521271E-8</v>
+        <v>0.4944319929665682</v>
       </c>
       <c r="T3">
-        <v>3.8306663382632432E-8</v>
+        <v>0.49861545276560998</v>
       </c>
       <c r="U3">
-        <v>3.8630781539580882E-8</v>
+        <v>0.50283430941626972</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>3.2556818543720473E-2</v>
+        <v>3.503668763102729E-2</v>
       </c>
       <c r="B4">
-        <v>3.2916168885796718E-8</v>
+        <v>0.42845053583398129</v>
       </c>
       <c r="C4">
-        <v>3.3194677297936448E-8</v>
+        <v>0.43207571708850551</v>
       </c>
       <c r="D4">
-        <v>3.347554220957957E-8</v>
+        <v>0.43573157152004538</v>
       </c>
       <c r="E4">
-        <v>3.3758783559405359E-8</v>
+        <v>0.4394183586587383</v>
       </c>
       <c r="F4">
-        <v>3.4044421454797118E-8</v>
+        <v>0.44313634023064291</v>
       </c>
       <c r="G4">
-        <v>3.4332476173269621E-8</v>
+        <v>0.44688578017631969</v>
       </c>
       <c r="H4">
-        <v>3.4622968163908573E-8</v>
+        <v>0.4506669446695678</v>
       </c>
       <c r="I4">
-        <v>3.4915918048822278E-8</v>
+        <v>0.45448010213632101</v>
       </c>
       <c r="J4">
-        <v>3.5211346624605729E-8</v>
+        <v>0.45832552327370341</v>
       </c>
       <c r="K4">
-        <v>3.5509274863816831E-8</v>
+        <v>0.46220348106924591</v>
       </c>
       <c r="L4">
-        <v>3.5809723916465319E-8</v>
+        <v>0.46611425082026642</v>
       </c>
       <c r="M4">
-        <v>3.6112715111514163E-8</v>
+        <v>0.47005811015341231</v>
       </c>
       <c r="N4">
-        <v>3.6418269958393737E-8</v>
+        <v>0.47403533904436979</v>
       </c>
       <c r="O4">
-        <v>3.6726410148528848E-8</v>
+        <v>0.47804621983773993</v>
       </c>
       <c r="P4">
-        <v>3.7037157556878472E-8</v>
+        <v>0.4820910372670813</v>
       </c>
       <c r="Q4">
-        <v>3.7350534243488731E-8</v>
+        <v>0.48617007847512372</v>
       </c>
       <c r="R4">
-        <v>3.7666562455059049E-8</v>
+        <v>0.49028363303415318</v>
       </c>
       <c r="S4">
-        <v>3.7985264626521271E-8</v>
+        <v>0.4944319929665682</v>
       </c>
       <c r="T4">
-        <v>3.8306663382632432E-8</v>
+        <v>0.49861545276560998</v>
       </c>
       <c r="U4">
-        <v>3.8630781539580882E-8</v>
+        <v>0.50283430941626972</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>5.064393934148978E-2</v>
+        <v>5.0052410901467607E-2</v>
       </c>
       <c r="B5">
-        <v>3.2916168885796718E-8</v>
+        <v>0.42845053583398129</v>
       </c>
       <c r="C5">
-        <v>3.3194677297936448E-8</v>
+        <v>0.43207571708850551</v>
       </c>
       <c r="D5">
-        <v>3.347554220957957E-8</v>
+        <v>0.43573157152004538</v>
       </c>
       <c r="E5">
-        <v>3.3758783559405359E-8</v>
+        <v>0.4394183586587383</v>
       </c>
       <c r="F5">
-        <v>3.4044421454797118E-8</v>
+        <v>0.44313634023064291</v>
       </c>
       <c r="G5">
-        <v>3.4332476173269621E-8</v>
+        <v>0.44688578017631969</v>
       </c>
       <c r="H5">
-        <v>3.4622968163908573E-8</v>
+        <v>0.4506669446695678</v>
       </c>
       <c r="I5">
-        <v>3.4915918048822278E-8</v>
+        <v>0.45448010213632101</v>
       </c>
       <c r="J5">
-        <v>3.5211346624605729E-8</v>
+        <v>0.45832552327370341</v>
       </c>
       <c r="K5">
-        <v>3.5509274863816831E-8</v>
+        <v>0.46220348106924591</v>
       </c>
       <c r="L5">
-        <v>3.5809723916465319E-8</v>
+        <v>0.46611425082026642</v>
       </c>
       <c r="M5">
-        <v>3.6112715111514163E-8</v>
+        <v>0.47005811015341231</v>
       </c>
       <c r="N5">
-        <v>3.6418269958393737E-8</v>
+        <v>0.47403533904436979</v>
       </c>
       <c r="O5">
-        <v>3.6726410148528848E-8</v>
+        <v>0.47804621983773993</v>
       </c>
       <c r="P5">
-        <v>3.7037157556878472E-8</v>
+        <v>0.4820910372670813</v>
       </c>
       <c r="Q5">
-        <v>3.7350534243488731E-8</v>
+        <v>0.48617007847512372</v>
       </c>
       <c r="R5">
-        <v>3.7666562455059049E-8</v>
+        <v>0.49028363303415318</v>
       </c>
       <c r="S5">
-        <v>3.7985264626521271E-8</v>
+        <v>0.4944319929665682</v>
       </c>
       <c r="T5">
-        <v>3.8306663382632432E-8</v>
+        <v>0.49861545276560998</v>
       </c>
       <c r="U5">
-        <v>3.8630781539580882E-8</v>
+        <v>0.50283430941626972</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>7.3554293644355895E-2</v>
+        <v>6.6069182389937156E-2</v>
       </c>
       <c r="B6">
-        <v>3.2780702457220548E-8</v>
+        <v>0.42695767682410668</v>
       </c>
       <c r="C6">
-        <v>3.3058064668535647E-8</v>
+        <v>0.43057022678506102</v>
       </c>
       <c r="D6">
-        <v>3.3337773681185029E-8</v>
+        <v>0.43421334304784998</v>
       </c>
       <c r="E6">
-        <v>3.3619849351790393E-8</v>
+        <v>0.4378872842383244</v>
       </c>
       <c r="F6">
-        <v>3.390431170498316E-8</v>
+        <v>0.44159231117060571</v>
       </c>
       <c r="G6">
-        <v>3.4191180934826002E-8</v>
+        <v>0.44532868686560062</v>
       </c>
       <c r="H6">
-        <v>3.4480477406246463E-8</v>
+        <v>0.44909667656967373</v>
       </c>
       <c r="I6">
-        <v>3.4772221656482618E-8</v>
+        <v>0.45289654777347649</v>
       </c>
       <c r="J6">
-        <v>3.5066434396541092E-8</v>
+        <v>0.4567285702309376</v>
       </c>
       <c r="K6">
-        <v>3.5363136512667268E-8</v>
+        <v>0.46059301597841212</v>
       </c>
       <c r="L6">
-        <v>3.5662349067828083E-8</v>
+        <v>0.46449015935399351</v>
       </c>
       <c r="M6">
-        <v>3.5964093303207173E-8</v>
+        <v>0.46842027701698902</v>
       </c>
       <c r="N6">
-        <v>3.6268390639712921E-8</v>
+        <v>0.47238364796755999</v>
       </c>
       <c r="O6">
-        <v>3.6575262679499081E-8</v>
+        <v>0.47638055356652809</v>
       </c>
       <c r="P6">
-        <v>3.6884731207498302E-8</v>
+        <v>0.48041127755534918</v>
       </c>
       <c r="Q6">
-        <v>3.7196818192968638E-8</v>
+        <v>0.48447610607625552</v>
       </c>
       <c r="R6">
-        <v>3.7511545791053237E-8</v>
+        <v>0.48857532769257062</v>
       </c>
       <c r="S6">
-        <v>3.7828936344353059E-8</v>
+        <v>0.49270923340919309</v>
       </c>
       <c r="T6">
-        <v>3.8149012384512972E-8</v>
+        <v>0.49687811669325582</v>
       </c>
       <c r="U6">
-        <v>3.8471796633821337E-8</v>
+        <v>0.5010822734949586</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>9.0435606758185835E-2</v>
+        <v>8.5089098532494897E-2</v>
       </c>
       <c r="B7">
-        <v>3.2374303171492047E-8</v>
+        <v>0.41800052276485972</v>
       </c>
       <c r="C7">
-        <v>3.2648226780333207E-8</v>
+        <v>0.42153728496439541</v>
       </c>
       <c r="D7">
-        <v>3.2924468096001392E-8</v>
+        <v>0.42510397221467833</v>
       </c>
       <c r="E7">
-        <v>3.3203046728945488E-8</v>
+        <v>0.42870083771584211</v>
       </c>
       <c r="F7">
-        <v>3.3483982455541252E-8</v>
+        <v>0.43232813681038318</v>
       </c>
       <c r="G7">
-        <v>3.3767295219495127E-8</v>
+        <v>0.4359861270012873</v>
       </c>
       <c r="H7">
-        <v>3.4053005133260132E-8</v>
+        <v>0.43967506797030992</v>
       </c>
       <c r="I7">
-        <v>3.4341132479463607E-8</v>
+        <v>0.44339522159641059</v>
       </c>
       <c r="J7">
-        <v>3.463169771234716E-8</v>
+        <v>0.44714685197434462</v>
       </c>
       <c r="K7">
-        <v>3.4924721459218592E-8</v>
+        <v>0.45093022543341038</v>
       </c>
       <c r="L7">
-        <v>3.522022452191635E-8</v>
+        <v>0.45474561055635732</v>
       </c>
       <c r="M7">
-        <v>3.551822787828619E-8</v>
+        <v>0.45859327819845092</v>
       </c>
       <c r="N7">
-        <v>3.5818752683670433E-8</v>
+        <v>0.46247350150670208</v>
       </c>
       <c r="O7">
-        <v>3.6121820272409753E-8</v>
+        <v>0.46638655593925832</v>
       </c>
       <c r="P7">
-        <v>3.6427452159357772E-8</v>
+        <v>0.47033271928495718</v>
       </c>
       <c r="Q7">
-        <v>3.673567004140833E-8</v>
+        <v>0.47431227168304729</v>
       </c>
       <c r="R7">
-        <v>3.7046495799035807E-8</v>
+        <v>0.47832549564307619</v>
       </c>
       <c r="S7">
-        <v>3.7359951497848398E-8</v>
+        <v>0.48237267606494438</v>
       </c>
       <c r="T7">
-        <v>3.7676059390154567E-8</v>
+        <v>0.48645410025913149</v>
       </c>
       <c r="U7">
-        <v>3.7994841916542737E-8</v>
+        <v>0.49057005796709219</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>0.1049053031194674</v>
+        <v>9.9103773584905741E-2</v>
       </c>
       <c r="B8">
-        <v>3.196790388576354E-8</v>
+        <v>0.41352194573523582</v>
       </c>
       <c r="C8">
-        <v>3.2238388892130773E-8</v>
+        <v>0.41702081405406233</v>
       </c>
       <c r="D8">
-        <v>3.2511162510817762E-8</v>
+        <v>0.42054928679809211</v>
       </c>
       <c r="E8">
-        <v>3.2786244106100603E-8</v>
+        <v>0.42410761445460049</v>
       </c>
       <c r="F8">
-        <v>3.3063653206099351E-8</v>
+        <v>0.42769604963027158</v>
       </c>
       <c r="G8">
-        <v>3.3343409504164252E-8</v>
+        <v>0.43131484706913031</v>
       </c>
       <c r="H8">
-        <v>3.3625532860273802E-8</v>
+        <v>0.43496426367062763</v>
       </c>
       <c r="I8">
-        <v>3.3910043302444623E-8</v>
+        <v>0.43864455850787731</v>
       </c>
       <c r="J8">
-        <v>3.4196961028153227E-8</v>
+        <v>0.4423559928460476</v>
       </c>
       <c r="K8">
-        <v>3.4486306405769903E-8</v>
+        <v>0.44609883016090918</v>
       </c>
       <c r="L8">
-        <v>3.4778099976004623E-8</v>
+        <v>0.44987333615753877</v>
       </c>
       <c r="M8">
-        <v>3.5072362453365208E-8</v>
+        <v>0.45367977878918131</v>
       </c>
       <c r="N8">
-        <v>3.5369114727627918E-8</v>
+        <v>0.45751842827627281</v>
       </c>
       <c r="O8">
-        <v>3.5668377865320432E-8</v>
+        <v>0.46138955712562302</v>
       </c>
       <c r="P8">
-        <v>3.5970173111217262E-8</v>
+        <v>0.46529344014976082</v>
       </c>
       <c r="Q8">
-        <v>3.6274521889848023E-8</v>
+        <v>0.46923035448644279</v>
       </c>
       <c r="R8">
-        <v>3.6581445807018371E-8</v>
+        <v>0.47320057961832851</v>
       </c>
       <c r="S8">
-        <v>3.6890966651343738E-8</v>
+        <v>0.47720439739281961</v>
       </c>
       <c r="T8">
-        <v>3.7203106395796169E-8</v>
+        <v>0.48124209204206891</v>
       </c>
       <c r="U8">
-        <v>3.7517887199264149E-8</v>
+        <v>0.48531395020315871</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>0.1193750008654185</v>
+        <v>0.11512054507337539</v>
       </c>
       <c r="B9">
-        <v>3.1426038171458909E-8</v>
+        <v>0.40307193266611491</v>
       </c>
       <c r="C9">
-        <v>3.1691938374527572E-8</v>
+        <v>0.40648238192995301</v>
       </c>
       <c r="D9">
-        <v>3.1960088397239617E-8</v>
+        <v>0.40992168749272567</v>
       </c>
       <c r="E9">
-        <v>3.2230507275640791E-8</v>
+        <v>0.41339009351170508</v>
       </c>
       <c r="F9">
-        <v>3.2503214206843539E-8</v>
+        <v>0.41688784621001262</v>
       </c>
       <c r="G9">
-        <v>3.2778228550389797E-8</v>
+        <v>0.42041519389409882</v>
       </c>
       <c r="H9">
-        <v>3.3055569829625421E-8</v>
+        <v>0.42397238697137052</v>
       </c>
       <c r="I9">
-        <v>3.3335257733086012E-8</v>
+        <v>0.42755967796796768</v>
       </c>
       <c r="J9">
-        <v>3.361731211589471E-8</v>
+        <v>0.43117732154668958</v>
       </c>
       <c r="K9">
-        <v>3.3901753001171723E-8</v>
+        <v>0.43482557452507459</v>
       </c>
       <c r="L9">
-        <v>3.4188600581455707E-8</v>
+        <v>0.4385046958936305</v>
       </c>
       <c r="M9">
-        <v>3.4477875220137288E-8</v>
+        <v>0.44221494683422069</v>
       </c>
       <c r="N9">
-        <v>3.4769597452904659E-8</v>
+        <v>0.44595659073860588</v>
       </c>
       <c r="O9">
-        <v>3.5063787989201389E-8</v>
+        <v>0.44972989322714219</v>
       </c>
       <c r="P9">
-        <v>3.5360467713696627E-8</v>
+        <v>0.45353512216763753</v>
       </c>
       <c r="Q9">
-        <v>3.5659657687767668E-8</v>
+        <v>0.45737254769436742</v>
       </c>
       <c r="R9">
-        <v>3.5961379150995189E-8</v>
+        <v>0.4612424422272523</v>
       </c>
       <c r="S9">
-        <v>3.6265653522670938E-8</v>
+        <v>0.46514508049119668</v>
       </c>
       <c r="T9">
-        <v>3.657250240331837E-8</v>
+        <v>0.46908073953559137</v>
       </c>
       <c r="U9">
-        <v>3.6881947576226077E-8</v>
+        <v>0.47304969875398212</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>0.13505050491063941</v>
+        <v>0.12713312368972679</v>
       </c>
       <c r="B10">
-        <v>3.0748706028578023E-8</v>
+        <v>0.39859335563649112</v>
       </c>
       <c r="C10">
-        <v>3.1008875227523459E-8</v>
+        <v>0.4019659110196197</v>
       </c>
       <c r="D10">
-        <v>3.1271245755266838E-8</v>
+        <v>0.40536700207613952</v>
       </c>
       <c r="E10">
-        <v>3.1535836237565907E-8</v>
+        <v>0.40879687025046352</v>
       </c>
       <c r="F10">
-        <v>3.1802665457773642E-8</v>
+        <v>0.41225575902990103</v>
       </c>
       <c r="G10">
-        <v>3.2071752358171632E-8</v>
+        <v>0.41574391396194171</v>
       </c>
       <c r="H10">
-        <v>3.2343116041314817E-8</v>
+        <v>0.41926158267168823</v>
       </c>
       <c r="I10">
-        <v>3.2616775771387622E-8</v>
+        <v>0.42280901487943418</v>
       </c>
       <c r="J10">
-        <v>3.2892750975571443E-8</v>
+        <v>0.42638646241839268</v>
       </c>
       <c r="K10">
-        <v>3.3171061245423862E-8</v>
+        <v>0.42999417925257338</v>
       </c>
       <c r="L10">
-        <v>3.3451726338269449E-8</v>
+        <v>0.43363242149481201</v>
       </c>
       <c r="M10">
-        <v>3.3734766178602279E-8</v>
+        <v>0.43730144742495108</v>
       </c>
       <c r="N10">
-        <v>3.4020200859500452E-8</v>
+        <v>0.44100151750817651</v>
       </c>
       <c r="O10">
-        <v>3.4308050644052461E-8</v>
+        <v>0.44473289441350689</v>
       </c>
       <c r="P10">
-        <v>3.4598335966795711E-8</v>
+        <v>0.44849584303244122</v>
       </c>
       <c r="Q10">
-        <v>3.4891077435167107E-8</v>
+        <v>0.45229063049776291</v>
       </c>
       <c r="R10">
-        <v>3.5186295830966082E-8</v>
+        <v>0.45611752620250462</v>
       </c>
       <c r="S10">
-        <v>3.5484012111829789E-8</v>
+        <v>0.4599768018190718</v>
       </c>
       <c r="T10">
-        <v>3.5784247412720993E-8</v>
+        <v>0.46386873131852868</v>
       </c>
       <c r="U10">
-        <v>3.6087023047428361E-8</v>
+        <v>0.46779359099004852</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>0.1531376270930784</v>
+        <v>0.14314989517819651</v>
       </c>
       <c r="B11">
-        <v>3.0206840314273393E-8</v>
+        <v>0.39411477860686789</v>
       </c>
       <c r="C11">
-        <v>3.0462424709920258E-8</v>
+        <v>0.39744944010928729</v>
       </c>
       <c r="D11">
-        <v>3.0720171641688713E-8</v>
+        <v>0.40081231665955408</v>
       </c>
       <c r="E11">
-        <v>3.0980099407106102E-8</v>
+        <v>0.40420364698922279</v>
       </c>
       <c r="F11">
-        <v>3.1242226458517829E-8</v>
+        <v>0.40762367184979009</v>
       </c>
       <c r="G11">
-        <v>3.1506571404397178E-8</v>
+        <v>0.41107263402978539</v>
       </c>
       <c r="H11">
-        <v>3.1773153010666443E-8</v>
+        <v>0.41455077837200682</v>
       </c>
       <c r="I11">
-        <v>3.2041990202029011E-8</v>
+        <v>0.41805835179090173</v>
       </c>
       <c r="J11">
-        <v>3.2313102063312919E-8</v>
+        <v>0.4215956032900966</v>
       </c>
       <c r="K11">
-        <v>3.2586507840825682E-8</v>
+        <v>0.42516278398007301</v>
       </c>
       <c r="L11">
-        <v>3.2862226943720533E-8</v>
+        <v>0.4287601470959943</v>
       </c>
       <c r="M11">
-        <v>3.3140278945374359E-8</v>
+        <v>0.43238794801568248</v>
       </c>
       <c r="N11">
-        <v>3.3420683584777167E-8</v>
+        <v>0.43604644427774802</v>
       </c>
       <c r="O11">
-        <v>3.3703460767933419E-8</v>
+        <v>0.43973589559987242</v>
       </c>
       <c r="P11">
-        <v>3.3988630569275083E-8</v>
+        <v>0.44345656389724558</v>
       </c>
       <c r="Q11">
-        <v>3.4276213233086758E-8</v>
+        <v>0.44720871330115919</v>
       </c>
       <c r="R11">
-        <v>3.4566229174942893E-8</v>
+        <v>0.45099261017775782</v>
       </c>
       <c r="S11">
-        <v>3.4858698983156983E-8</v>
+        <v>0.45480852314694792</v>
       </c>
       <c r="T11">
-        <v>3.5153643420243188E-8</v>
+        <v>0.45865672310146721</v>
       </c>
       <c r="U11">
-        <v>3.5451083424390288E-8</v>
+        <v>0.46253748322611588</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>0.16760732345435991</v>
+        <v>0.15816561844863611</v>
       </c>
       <c r="B12">
-        <v>2.9800441028544878E-8</v>
+        <v>0.38366476553774631</v>
       </c>
       <c r="C12">
-        <v>3.0052586821717817E-8</v>
+        <v>0.3869110079851773</v>
       </c>
       <c r="D12">
-        <v>3.0306866056505083E-8</v>
+        <v>0.39018471735418692</v>
       </c>
       <c r="E12">
-        <v>3.056329678426121E-8</v>
+        <v>0.39348612604632649</v>
       </c>
       <c r="F12">
-        <v>3.0821897209075928E-8</v>
+        <v>0.39681546842953042</v>
       </c>
       <c r="G12">
-        <v>3.1082685689066322E-8</v>
+        <v>0.40017298085475311</v>
       </c>
       <c r="H12">
-        <v>3.1345680737680119E-8</v>
+        <v>0.40355890167274883</v>
       </c>
       <c r="I12">
-        <v>3.1610901025010007E-8</v>
+        <v>0.40697347125099131</v>
       </c>
       <c r="J12">
-        <v>3.1878365379118987E-8</v>
+        <v>0.41041693199073781</v>
       </c>
       <c r="K12">
-        <v>3.2148092787376993E-8</v>
+        <v>0.41388952834423748</v>
       </c>
       <c r="L12">
-        <v>3.2420102397808813E-8</v>
+        <v>0.4173915068320852</v>
       </c>
       <c r="M12">
-        <v>3.2694413520453383E-8</v>
+        <v>0.42092311606072103</v>
       </c>
       <c r="N12">
-        <v>3.2971045628734679E-8</v>
+        <v>0.42448460674008032</v>
       </c>
       <c r="O12">
-        <v>3.3250018360844098E-8</v>
+        <v>0.42807623170139081</v>
       </c>
       <c r="P12">
-        <v>3.3531351521134573E-8</v>
+        <v>0.43169824591512151</v>
       </c>
       <c r="Q12">
-        <v>3.3815065081526458E-8</v>
+        <v>0.43535090650908292</v>
       </c>
       <c r="R12">
-        <v>3.4101179182925463E-8</v>
+        <v>0.43903447278668067</v>
       </c>
       <c r="S12">
-        <v>3.4389714136652329E-8</v>
+        <v>0.44274920624532399</v>
       </c>
       <c r="T12">
-        <v>3.4680690425884789E-8</v>
+        <v>0.44649537059498862</v>
       </c>
       <c r="U12">
-        <v>3.4974128707111701E-8</v>
+        <v>0.4502732317769384</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>0.18328282888425049</v>
+        <v>0.1721802935010471</v>
       </c>
       <c r="B13">
-        <v>2.966497459996866E-8</v>
+        <v>0.38366476553774631</v>
       </c>
       <c r="C13">
-        <v>2.9915974192316958E-8</v>
+        <v>0.3869110079851773</v>
       </c>
       <c r="D13">
-        <v>3.0169097528110482E-8</v>
+        <v>0.39018471735418692</v>
       </c>
       <c r="E13">
-        <v>3.0424362576646191E-8</v>
+        <v>0.39348612604632649</v>
       </c>
       <c r="F13">
-        <v>3.0681787459261897E-8</v>
+        <v>0.39681546842953042</v>
       </c>
       <c r="G13">
-        <v>3.0941390450622631E-8</v>
+        <v>0.40017298085475311</v>
       </c>
       <c r="H13">
-        <v>3.1203189980017963E-8</v>
+        <v>0.40355890167274883</v>
       </c>
       <c r="I13">
-        <v>3.1467204632670288E-8</v>
+        <v>0.40697347125099131</v>
       </c>
       <c r="J13">
-        <v>3.173345315105429E-8</v>
+        <v>0.41041693199073781</v>
       </c>
       <c r="K13">
-        <v>3.2001954436227371E-8</v>
+        <v>0.41388952834423748</v>
       </c>
       <c r="L13">
-        <v>3.2272727549171511E-8</v>
+        <v>0.4173915068320852</v>
       </c>
       <c r="M13">
-        <v>3.2545791712146327E-8</v>
+        <v>0.42092311606072103</v>
       </c>
       <c r="N13">
-        <v>3.282116631005379E-8</v>
+        <v>0.42448460674008032</v>
       </c>
       <c r="O13">
-        <v>3.3098870891814258E-8</v>
+        <v>0.42807623170139081</v>
       </c>
       <c r="P13">
-        <v>3.337892517175433E-8</v>
+        <v>0.43169824591512151</v>
       </c>
       <c r="Q13">
-        <v>3.3661349031006291E-8</v>
+        <v>0.43535090650908292</v>
       </c>
       <c r="R13">
-        <v>3.3946162518919578E-8</v>
+        <v>0.43903447278668067</v>
       </c>
       <c r="S13">
-        <v>3.4233385854484051E-8</v>
+        <v>0.44274920624532399</v>
       </c>
       <c r="T13">
-        <v>3.4523039427765257E-8</v>
+        <v>0.44649537059498862</v>
       </c>
       <c r="U13">
-        <v>3.4815143801352097E-8</v>
+        <v>0.4502732317769384</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>0.19654671756159259</v>
+        <v>0.1881970649895168</v>
       </c>
       <c r="B14">
-        <v>2.966497459996866E-8</v>
+        <v>0.38515762454762098</v>
       </c>
       <c r="C14">
-        <v>2.9915974192316958E-8</v>
+        <v>0.38841649828862168</v>
       </c>
       <c r="D14">
-        <v>3.0169097528110482E-8</v>
+        <v>0.39170294582638238</v>
       </c>
       <c r="E14">
-        <v>3.0424362576646191E-8</v>
+        <v>0.39501720046674038</v>
       </c>
       <c r="F14">
-        <v>3.0681787459261897E-8</v>
+        <v>0.39835949748956762</v>
       </c>
       <c r="G14">
-        <v>3.0941390450622631E-8</v>
+        <v>0.40173007416547207</v>
       </c>
       <c r="H14">
-        <v>3.1203189980017963E-8</v>
+        <v>0.40512916977264302</v>
       </c>
       <c r="I14">
-        <v>3.1467204632670288E-8</v>
+        <v>0.40855702561383572</v>
       </c>
       <c r="J14">
-        <v>3.173345315105429E-8</v>
+        <v>0.41201388503350339</v>
       </c>
       <c r="K14">
-        <v>3.2001954436227371E-8</v>
+        <v>0.41549999343507132</v>
       </c>
       <c r="L14">
-        <v>3.2272727549171511E-8</v>
+        <v>0.41901559829835799</v>
       </c>
       <c r="M14">
-        <v>3.2545791712146327E-8</v>
+        <v>0.42256094919714421</v>
       </c>
       <c r="N14">
-        <v>3.282116631005379E-8</v>
+        <v>0.42613629781689011</v>
       </c>
       <c r="O14">
-        <v>3.3098870891814258E-8</v>
+        <v>0.42974189797260259</v>
       </c>
       <c r="P14">
-        <v>3.337892517175433E-8</v>
+        <v>0.43337800562685369</v>
       </c>
       <c r="Q14">
-        <v>3.3661349031006291E-8</v>
+        <v>0.43704487890795107</v>
       </c>
       <c r="R14">
-        <v>3.3946162518919578E-8</v>
+        <v>0.44074277812826329</v>
       </c>
       <c r="S14">
-        <v>3.4233385854484051E-8</v>
+        <v>0.44447196580269899</v>
       </c>
       <c r="T14">
-        <v>3.4523039427765257E-8</v>
+        <v>0.44823270666734288</v>
       </c>
       <c r="U14">
-        <v>3.4815143801352097E-8</v>
+        <v>0.45202526769824958</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>0.2110164139228741</v>
+        <v>0.20321278825995781</v>
       </c>
       <c r="B15">
-        <v>2.9935907457120988E-8</v>
+        <v>0.38963620157724399</v>
       </c>
       <c r="C15">
-        <v>3.0189199451118578E-8</v>
+        <v>0.3929329691989541</v>
       </c>
       <c r="D15">
-        <v>3.0444634584899558E-8</v>
+        <v>0.39625763124296781</v>
       </c>
       <c r="E15">
-        <v>3.0702230991876117E-8</v>
+        <v>0.39961042372798122</v>
       </c>
       <c r="F15">
-        <v>3.096200695888984E-8</v>
+        <v>0.40299158466967838</v>
       </c>
       <c r="G15">
-        <v>3.1223980927509881E-8</v>
+        <v>0.40640135409762829</v>
       </c>
       <c r="H15">
-        <v>3.148817149534217E-8</v>
+        <v>0.40983997407232442</v>
       </c>
       <c r="I15">
-        <v>3.175459741734962E-8</v>
+        <v>0.41330768870236828</v>
       </c>
       <c r="J15">
-        <v>3.2023277607183571E-8</v>
+        <v>0.41680474416179952</v>
       </c>
       <c r="K15">
-        <v>3.229423113852649E-8</v>
+        <v>0.4203313887075717</v>
       </c>
       <c r="L15">
-        <v>3.2567477246445989E-8</v>
+        <v>0.42388787269717582</v>
       </c>
       <c r="M15">
-        <v>3.284303532876032E-8</v>
+        <v>0.42747444860641293</v>
       </c>
       <c r="N15">
-        <v>3.3120924947415462E-8</v>
+        <v>0.43109137104731859</v>
       </c>
       <c r="O15">
-        <v>3.3401165829873812E-8</v>
+        <v>0.43473889678623712</v>
       </c>
       <c r="P15">
-        <v>3.368377787051467E-8</v>
+        <v>0.43841728476204922</v>
       </c>
       <c r="Q15">
-        <v>3.3968781132046492E-8</v>
+        <v>0.44212679610455469</v>
       </c>
       <c r="R15">
-        <v>3.4256195846931202E-8</v>
+        <v>0.44586769415301009</v>
       </c>
       <c r="S15">
-        <v>3.4546042418820481E-8</v>
+        <v>0.44964024447482298</v>
       </c>
       <c r="T15">
-        <v>3.4838341424004189E-8</v>
+        <v>0.45344471488440452</v>
       </c>
       <c r="U15">
-        <v>3.5133113612871173E-8</v>
+        <v>0.45728137546218228</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>0.22186868723233741</v>
+        <v>0.21722746331236881</v>
       </c>
       <c r="B16">
-        <v>3.0748706028578023E-8</v>
+        <v>0.40157907365624029</v>
       </c>
       <c r="C16">
-        <v>3.1008875227523459E-8</v>
+        <v>0.40497689162650857</v>
       </c>
       <c r="D16">
-        <v>3.1271245755266838E-8</v>
+        <v>0.40840345902053038</v>
       </c>
       <c r="E16">
-        <v>3.1535836237565907E-8</v>
+        <v>0.4118590190912913</v>
       </c>
       <c r="F16">
-        <v>3.1802665457773642E-8</v>
+        <v>0.41534381714997543</v>
       </c>
       <c r="G16">
-        <v>3.2071752358171632E-8</v>
+        <v>0.41885810058337969</v>
       </c>
       <c r="H16">
-        <v>3.2343116041314817E-8</v>
+        <v>0.42240211887147638</v>
       </c>
       <c r="I16">
-        <v>3.2616775771387622E-8</v>
+        <v>0.42597612360512321</v>
       </c>
       <c r="J16">
-        <v>3.2892750975571443E-8</v>
+        <v>0.42958036850392411</v>
       </c>
       <c r="K16">
-        <v>3.3171061245423862E-8</v>
+        <v>0.43321510943424102</v>
       </c>
       <c r="L16">
-        <v>3.3451726338269449E-8</v>
+        <v>0.43688060442735782</v>
       </c>
       <c r="M16">
-        <v>3.3734766178602279E-8</v>
+        <v>0.44057711369779762</v>
       </c>
       <c r="N16">
-        <v>3.4020200859500452E-8</v>
+        <v>0.44430489966179609</v>
       </c>
       <c r="O16">
-        <v>3.4308050644052461E-8</v>
+        <v>0.44806422695593051</v>
       </c>
       <c r="P16">
-        <v>3.4598335966795711E-8</v>
+        <v>0.45185536245590552</v>
       </c>
       <c r="Q16">
-        <v>3.4891077435167107E-8</v>
+        <v>0.45567857529549932</v>
       </c>
       <c r="R16">
-        <v>3.5186295830966082E-8</v>
+        <v>0.45953413688566969</v>
       </c>
       <c r="S16">
-        <v>3.5484012111829789E-8</v>
+        <v>0.46342232093382169</v>
       </c>
       <c r="T16">
-        <v>3.5784247412720993E-8</v>
+        <v>0.46734340346323722</v>
       </c>
       <c r="U16">
-        <v>3.6087023047428361E-8</v>
+        <v>0.47129766283267088</v>
       </c>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>0.23151515147319179</v>
+        <v>0.2272379454926623</v>
       </c>
       <c r="B17">
-        <v>3.1426038171458909E-8</v>
+        <v>0.41501480474511038</v>
       </c>
       <c r="C17">
-        <v>3.1691938374527572E-8</v>
+        <v>0.4185263043575066</v>
       </c>
       <c r="D17">
-        <v>3.1960088397239617E-8</v>
+        <v>0.42206751527028752</v>
       </c>
       <c r="E17">
-        <v>3.2230507275640791E-8</v>
+        <v>0.42563868887501433</v>
       </c>
       <c r="F17">
-        <v>3.2503214206843539E-8</v>
+        <v>0.42924007869030872</v>
       </c>
       <c r="G17">
-        <v>3.2778228550389797E-8</v>
+        <v>0.43287194037984927</v>
       </c>
       <c r="H17">
-        <v>3.3055569829625421E-8</v>
+        <v>0.43653453177052171</v>
       </c>
       <c r="I17">
-        <v>3.3335257733086012E-8</v>
+        <v>0.44022811287072172</v>
       </c>
       <c r="J17">
-        <v>3.361731211589471E-8</v>
+        <v>0.44395294588881329</v>
       </c>
       <c r="K17">
-        <v>3.3901753001171723E-8</v>
+        <v>0.44770929525174302</v>
       </c>
       <c r="L17">
-        <v>3.4188600581455707E-8</v>
+        <v>0.45149742762381168</v>
       </c>
       <c r="M17">
-        <v>3.4477875220137288E-8</v>
+        <v>0.45531761192560438</v>
       </c>
       <c r="N17">
-        <v>3.4769597452904659E-8</v>
+        <v>0.45917011935308261</v>
       </c>
       <c r="O17">
-        <v>3.5063787989201389E-8</v>
+        <v>0.4630552233968348</v>
       </c>
       <c r="P17">
-        <v>3.5360467713696627E-8</v>
+        <v>0.46697319986149288</v>
       </c>
       <c r="Q17">
-        <v>3.5659657687767668E-8</v>
+        <v>0.47092432688531111</v>
       </c>
       <c r="R17">
-        <v>3.5961379150995189E-8</v>
+        <v>0.47490888495991113</v>
       </c>
       <c r="S17">
-        <v>3.6265653522670938E-8</v>
+        <v>0.4789271569501945</v>
       </c>
       <c r="T17">
-        <v>3.657250240331837E-8</v>
+        <v>0.48297942811442313</v>
       </c>
       <c r="U17">
-        <v>3.6881947576226077E-8</v>
+        <v>0.48706598612446989</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>0.2399558080301068</v>
+        <v>0.24125262054507329</v>
       </c>
       <c r="B18">
-        <v>3.2238836742915931E-8</v>
+        <v>0.43143625385372991</v>
       </c>
       <c r="C18">
-        <v>3.2511614150932453E-8</v>
+        <v>0.43508669769539338</v>
       </c>
       <c r="D18">
-        <v>3.2786699567606897E-8</v>
+        <v>0.43876802846443552</v>
       </c>
       <c r="E18">
-        <v>3.3064112521330588E-8</v>
+        <v>0.44248050749956519</v>
       </c>
       <c r="F18">
-        <v>3.3343872705727347E-8</v>
+        <v>0.44622439835071659</v>
       </c>
       <c r="G18">
-        <v>3.3625999981051548E-8</v>
+        <v>0.44999996679775689</v>
       </c>
       <c r="H18">
-        <v>3.3910514375598082E-8</v>
+        <v>0.45380748086935518</v>
       </c>
       <c r="I18">
-        <v>3.4197436087124007E-8</v>
+        <v>0.45764721086200921</v>
       </c>
       <c r="J18">
-        <v>3.4486785484282568E-8</v>
+        <v>0.46151942935923379</v>
       </c>
       <c r="K18">
-        <v>3.4778583108069088E-8</v>
+        <v>0.46542441125091261</v>
       </c>
       <c r="L18">
-        <v>3.5072849673279167E-8</v>
+        <v>0.46936243375281128</v>
       </c>
       <c r="M18">
-        <v>3.536960606997926E-8</v>
+        <v>0.47333377642625779</v>
       </c>
       <c r="N18">
-        <v>3.5668873364989663E-8</v>
+        <v>0.47733872119798859</v>
       </c>
       <c r="O18">
-        <v>3.5970672803380039E-8</v>
+        <v>0.48137755238016272</v>
       </c>
       <c r="P18">
-        <v>3.6275025809977668E-8</v>
+        <v>0.48545055669054471</v>
       </c>
       <c r="Q18">
-        <v>3.6581953990888289E-8</v>
+        <v>0.48955802327285919</v>
       </c>
       <c r="R18">
-        <v>3.6891479135030061E-8</v>
+        <v>0.49370024371731752</v>
       </c>
       <c r="S18">
-        <v>3.7203623215680253E-8</v>
+        <v>0.49787751208131731</v>
       </c>
       <c r="T18">
-        <v>3.7518408392035167E-8</v>
+        <v>0.50209012491031746</v>
       </c>
       <c r="U18">
-        <v>3.7835857010783278E-8</v>
+        <v>0.5063383812588913</v>
       </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>0.2483964645870218</v>
+        <v>0.24926100628930811</v>
       </c>
       <c r="B19">
-        <v>3.3458034600101447E-8</v>
+        <v>0.44785770296234989</v>
       </c>
       <c r="C19">
-        <v>3.3741127815539748E-8</v>
+        <v>0.45164709103328099</v>
       </c>
       <c r="D19">
-        <v>3.4026616323157807E-8</v>
+        <v>0.45546854165858408</v>
       </c>
       <c r="E19">
-        <v>3.4314520389865283E-8</v>
+        <v>0.45932232612411672</v>
       </c>
       <c r="F19">
-        <v>3.460486045405305E-8</v>
+        <v>0.46320871801112512</v>
       </c>
       <c r="G19">
-        <v>3.4897657127044168E-8</v>
+        <v>0.46712799321566528</v>
       </c>
       <c r="H19">
-        <v>3.5192931194557053E-8</v>
+        <v>0.47108042996818938</v>
       </c>
       <c r="I19">
-        <v>3.5490703618181008E-8</v>
+        <v>0.47506630885329743</v>
       </c>
       <c r="J19">
-        <v>3.5790995536864359E-8</v>
+        <v>0.47908591282965518</v>
       </c>
       <c r="K19">
-        <v>3.6093828268415129E-8</v>
+        <v>0.48313952725008291</v>
       </c>
       <c r="L19">
-        <v>3.6399223311014347E-8</v>
+        <v>0.48722743988181172</v>
       </c>
       <c r="M19">
-        <v>3.6707202344742202E-8</v>
+        <v>0.49134994092691192</v>
       </c>
       <c r="N19">
-        <v>3.7017787233117128E-8</v>
+        <v>0.49550732304289541</v>
       </c>
       <c r="O19">
-        <v>3.7331000024648002E-8</v>
+        <v>0.49969988136349142</v>
       </c>
       <c r="P19">
-        <v>3.7646862954399213E-8</v>
+        <v>0.50392791351959731</v>
       </c>
       <c r="Q19">
-        <v>3.7965398445569212E-8</v>
+        <v>0.50819171966040821</v>
       </c>
       <c r="R19">
-        <v>3.8286629111082357E-8</v>
+        <v>0.51249160247472469</v>
       </c>
       <c r="S19">
-        <v>3.8610577755194202E-8</v>
+        <v>0.51682786721244067</v>
       </c>
       <c r="T19">
-        <v>3.893726737511035E-8</v>
+        <v>0.52120082170621262</v>
       </c>
       <c r="U19">
-        <v>3.9266721162619067E-8</v>
+        <v>0.52561077639331344</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>0.26045454558042452</v>
+        <v>0.25827044025157159</v>
       </c>
       <c r="B20">
-        <v>3.4812698885863087E-8</v>
+        <v>0.46726487009071782</v>
       </c>
       <c r="C20">
-        <v>3.5107254109547823E-8</v>
+        <v>0.47121846497805592</v>
       </c>
       <c r="D20">
-        <v>3.5404301607103212E-8</v>
+        <v>0.47520551179712223</v>
       </c>
       <c r="E20">
-        <v>3.5703862466014872E-8</v>
+        <v>0.47922629358949448</v>
       </c>
       <c r="F20">
-        <v>3.6005957952192658E-8</v>
+        <v>0.48328109579160661</v>
       </c>
       <c r="G20">
-        <v>3.6310609511480373E-8</v>
+        <v>0.4873702062550101</v>
       </c>
       <c r="H20">
-        <v>3.6617838771178082E-8</v>
+        <v>0.49149391526681041</v>
       </c>
       <c r="I20">
-        <v>3.6927667541577608E-8</v>
+        <v>0.49565251557027301</v>
       </c>
       <c r="J20">
-        <v>3.7240117817510728E-8</v>
+        <v>0.49984630238560629</v>
       </c>
       <c r="K20">
-        <v>3.7555211779910681E-8</v>
+        <v>0.50407557343091913</v>
       </c>
       <c r="L20">
-        <v>3.7872971797386697E-8</v>
+        <v>0.50834062894335619</v>
       </c>
       <c r="M20">
-        <v>3.8193420427812047E-8</v>
+        <v>0.5126417717004107</v>
       </c>
       <c r="N20">
-        <v>3.8516580419925377E-8</v>
+        <v>0.51697930704142026</v>
       </c>
       <c r="O20">
-        <v>3.8842474714945693E-8</v>
+        <v>0.52135354288924196</v>
       </c>
       <c r="P20">
-        <v>3.9171126448200868E-8</v>
+        <v>0.5257647897721125</v>
       </c>
       <c r="Q20">
-        <v>3.9502558950770162E-8</v>
+        <v>0.53021336084569182</v>
       </c>
       <c r="R20">
-        <v>3.9836795751140399E-8</v>
+        <v>0.53469957191529549</v>
       </c>
       <c r="S20">
-        <v>4.017386057687631E-8</v>
+        <v>0.53922374145831253</v>
       </c>
       <c r="T20">
-        <v>4.0513777356304932E-8</v>
+        <v>0.54378619064681444</v>
       </c>
       <c r="U20">
-        <v>4.0856570220214321E-8</v>
+        <v>0.54838724337035627</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>0.27010100982127883</v>
+        <v>0.26928197064989517</v>
       </c>
       <c r="B21">
-        <v>3.6302829600201008E-8</v>
+        <v>0.48667203721908642</v>
       </c>
       <c r="C21">
-        <v>3.6609993032956811E-8</v>
+        <v>0.49078983892283162</v>
       </c>
       <c r="D21">
-        <v>3.6919755419443278E-8</v>
+        <v>0.49494248193566093</v>
       </c>
       <c r="E21">
-        <v>3.7232138749779552E-8</v>
+        <v>0.49913026105487301</v>
       </c>
       <c r="F21">
-        <v>3.754716520014637E-8</v>
+        <v>0.50335347357208871</v>
       </c>
       <c r="G21">
-        <v>3.786485713436029E-8</v>
+        <v>0.50761241929435574</v>
       </c>
       <c r="H21">
-        <v>3.8185237105461333E-8</v>
+        <v>0.51190740056543194</v>
       </c>
       <c r="I21">
-        <v>3.8508327857314E-8</v>
+        <v>0.51623872228724932</v>
       </c>
       <c r="J21">
-        <v>3.8834152326221873E-8</v>
+        <v>0.52060669194155806</v>
       </c>
       <c r="K21">
-        <v>3.9162733642555901E-8</v>
+        <v>0.52501161961175624</v>
       </c>
       <c r="L21">
-        <v>3.9494095132396428E-8</v>
+        <v>0.52945381800490143</v>
       </c>
       <c r="M21">
-        <v>3.9828260319189041E-8</v>
+        <v>0.53393360247391042</v>
       </c>
       <c r="N21">
-        <v>4.0165252925414587E-8</v>
+        <v>0.53845129103994582</v>
       </c>
       <c r="O21">
-        <v>4.0505096874273271E-8</v>
+        <v>0.54300720441499339</v>
       </c>
       <c r="P21">
-        <v>4.0847816291382832E-8</v>
+        <v>0.54760166602462845</v>
       </c>
       <c r="Q21">
-        <v>4.1193435506491338E-8</v>
+        <v>0.55223500203097631</v>
       </c>
       <c r="R21">
-        <v>4.1541979055204379E-8</v>
+        <v>0.55690754135586706</v>
       </c>
       <c r="S21">
-        <v>4.1893471680726768E-8</v>
+        <v>0.56161961570418495</v>
       </c>
       <c r="T21">
-        <v>4.2247938335619113E-8</v>
+        <v>0.56637155958741703</v>
       </c>
       <c r="U21">
-        <v>4.2605404183569238E-8</v>
+        <v>0.57116371034739999</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>0.28457070756723002</v>
+        <v>0.27729035639413008</v>
       </c>
       <c r="B22">
-        <v>3.874122531457206E-8</v>
+        <v>0.5045863453375804</v>
       </c>
       <c r="C22">
-        <v>3.906902036217144E-8</v>
+        <v>0.50885572256416278</v>
       </c>
       <c r="D22">
-        <v>3.9399588930545098E-8</v>
+        <v>0.51316122360200433</v>
       </c>
       <c r="E22">
-        <v>3.9732954486848923E-8</v>
+        <v>0.51750315409983771</v>
       </c>
       <c r="F22">
-        <v>4.0069140696797782E-8</v>
+        <v>0.52188182229253366</v>
       </c>
       <c r="G22">
-        <v>4.0408171426345542E-8</v>
+        <v>0.52629753902298237</v>
       </c>
       <c r="H22">
-        <v>4.0750070743379302E-8</v>
+        <v>0.53075061776415955</v>
       </c>
       <c r="I22">
-        <v>4.1094862919428E-8</v>
+        <v>0.53524137464138111</v>
       </c>
       <c r="J22">
-        <v>4.1442572431385448E-8</v>
+        <v>0.53977012845474426</v>
       </c>
       <c r="K22">
-        <v>4.1793223963248002E-8</v>
+        <v>0.5443372007017595</v>
       </c>
       <c r="L22">
-        <v>4.2146842407866788E-8</v>
+        <v>0.54894291560017394</v>
       </c>
       <c r="M22">
-        <v>4.2503452868714911E-8</v>
+        <v>0.55358760011098684</v>
       </c>
       <c r="N22">
-        <v>4.2863080661669571E-8</v>
+        <v>0.55827158396166165</v>
       </c>
       <c r="O22">
-        <v>4.3225751316809211E-8</v>
+        <v>0.56299519966953293</v>
       </c>
       <c r="P22">
-        <v>4.3591490580225927E-8</v>
+        <v>0.56775878256541235</v>
       </c>
       <c r="Q22">
-        <v>4.3960324415853183E-8</v>
+        <v>0.57256267081739265</v>
       </c>
       <c r="R22">
-        <v>4.4332279007308977E-8</v>
+        <v>0.57740720545485591</v>
       </c>
       <c r="S22">
-        <v>4.4707380759754692E-8</v>
+        <v>0.58229273039268259</v>
       </c>
       <c r="T22">
-        <v>4.508565630176949E-8</v>
+        <v>0.58721959245566557</v>
       </c>
       <c r="U22">
-        <v>4.5467132487240822E-8</v>
+        <v>0.59218814140313258</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>0.29542297949202367</v>
+        <v>0.28629979035639358</v>
       </c>
       <c r="B23">
-        <v>4.104415460036693E-8</v>
+        <v>0.53444352553507057</v>
       </c>
       <c r="C23">
-        <v>4.1391435061985249E-8</v>
+        <v>0.53896552863304836</v>
       </c>
       <c r="D23">
-        <v>4.1741653913252378E-8</v>
+        <v>0.54352579304591009</v>
       </c>
       <c r="E23">
-        <v>4.2094836016303328E-8</v>
+        <v>0.54812464250811244</v>
       </c>
       <c r="F23">
-        <v>4.2451006443635243E-8</v>
+        <v>0.55276240349327566</v>
       </c>
       <c r="G23">
-        <v>4.2810190479887157E-8</v>
+        <v>0.55743940523736024</v>
       </c>
       <c r="H23">
-        <v>4.3172413623635141E-8</v>
+        <v>0.56215597976203913</v>
       </c>
       <c r="I23">
-        <v>4.3537701589202328E-8</v>
+        <v>0.56691246189826794</v>
       </c>
       <c r="J23">
-        <v>4.3906080308484392E-8</v>
+        <v>0.57170918931005488</v>
       </c>
       <c r="K23">
-        <v>4.4277575932790528E-8</v>
+        <v>0.57654650251843198</v>
       </c>
       <c r="L23">
-        <v>4.4652214834699913E-8</v>
+        <v>0.58142474492562835</v>
       </c>
       <c r="M23">
-        <v>4.5030023609933792E-8</v>
+        <v>0.58634426283944785</v>
       </c>
       <c r="N23">
-        <v>4.5411029079243712E-8</v>
+        <v>0.59130540549785482</v>
       </c>
       <c r="O23">
-        <v>4.5795258290315371E-8</v>
+        <v>0.59630852509376597</v>
       </c>
       <c r="P23">
-        <v>4.6182738519688859E-8</v>
+        <v>0.60135397680005243</v>
       </c>
       <c r="Q23">
-        <v>4.6573497274694908E-8</v>
+        <v>0.6064421187947534</v>
       </c>
       <c r="R23">
-        <v>4.6967562295407763E-8</v>
+        <v>0.61157331228650458</v>
       </c>
       <c r="S23">
-        <v>4.7364961556614392E-8</v>
+        <v>0.61674792154017899</v>
       </c>
       <c r="T23">
-        <v>4.7765723269800402E-8</v>
+        <v>0.6219663139027467</v>
       </c>
       <c r="U23">
-        <v>4.8169875885152848E-8</v>
+        <v>0.62722885982935372</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>0.30145202068105992</v>
+        <v>0.29731132075471722</v>
       </c>
       <c r="B24">
-        <v>4.2534285314704792E-8</v>
+        <v>0.56280784672268636</v>
       </c>
       <c r="C24">
-        <v>4.2894173985394177E-8</v>
+        <v>0.56756984439848968</v>
       </c>
       <c r="D24">
-        <v>4.3257107725592377E-8</v>
+        <v>0.57237213401762066</v>
       </c>
       <c r="E24">
-        <v>4.3623112300067949E-8</v>
+        <v>0.57721505649597338</v>
       </c>
       <c r="F24">
-        <v>4.3992213691588868E-8</v>
+        <v>0.5820989556339804</v>
       </c>
       <c r="G24">
-        <v>4.436443810276702E-8</v>
+        <v>0.58702417814101926</v>
       </c>
       <c r="H24">
-        <v>4.473981195791834E-8</v>
+        <v>0.59199107366002468</v>
       </c>
       <c r="I24">
-        <v>4.5118361904938647E-8</v>
+        <v>0.59699999479231025</v>
       </c>
       <c r="J24">
-        <v>4.5500114817195458E-8</v>
+        <v>0.60205129712259986</v>
       </c>
       <c r="K24">
-        <v>4.5885097795435702E-8</v>
+        <v>0.60714533924427072</v>
       </c>
       <c r="L24">
-        <v>4.6273338169709571E-8</v>
+        <v>0.6122824827848099</v>
       </c>
       <c r="M24">
-        <v>4.6664863501310713E-8</v>
+        <v>0.61746309243148578</v>
       </c>
       <c r="N24">
-        <v>4.7059701584732843E-8</v>
+        <v>0.62268753595723847</v>
       </c>
       <c r="O24">
-        <v>4.7457880449642889E-8</v>
+        <v>0.62795618424678734</v>
       </c>
       <c r="P24">
-        <v>4.7859428362870757E-8</v>
+        <v>0.63326941132296044</v>
       </c>
       <c r="Q24">
-        <v>4.8264373830416018E-8</v>
+        <v>0.63862759437324623</v>
       </c>
       <c r="R24">
-        <v>4.8672745599471683E-8</v>
+        <v>0.64403111377657074</v>
       </c>
       <c r="S24">
-        <v>4.9084572660464777E-8</v>
+        <v>0.6494803531303005</v>
       </c>
       <c r="T24">
-        <v>4.949988424911451E-8</v>
+        <v>0.65497569927747379</v>
       </c>
       <c r="U24">
-        <v>4.9918709848507713E-8</v>
+        <v>0.66051754233426374</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>0.31109848492191428</v>
+        <v>0.30632075471698073</v>
       </c>
       <c r="B25">
-        <v>4.4295348886194998E-8</v>
+        <v>0.58520073187080346</v>
       </c>
       <c r="C25">
-        <v>4.4670138167604739E-8</v>
+        <v>0.59015219895015336</v>
       </c>
       <c r="D25">
-        <v>4.5048098594721472E-8</v>
+        <v>0.5951455611005495</v>
       </c>
       <c r="E25">
-        <v>4.5429256999062502E-8</v>
+        <v>0.60018117280217875</v>
       </c>
       <c r="F25">
-        <v>4.5813640439170437E-8</v>
+        <v>0.60525939153453623</v>
       </c>
       <c r="G25">
-        <v>4.6201276202534127E-8</v>
+        <v>0.6103805778018021</v>
       </c>
       <c r="H25">
-        <v>4.6592191807525738E-8</v>
+        <v>0.6155450951584337</v>
       </c>
       <c r="I25">
-        <v>4.6986415005354312E-8</v>
+        <v>0.62075331023497471</v>
       </c>
       <c r="J25">
-        <v>4.7383973782035832E-8</v>
+        <v>0.62600559276408219</v>
       </c>
       <c r="K25">
-        <v>4.7784896360379982E-8</v>
+        <v>0.63130231560677441</v>
       </c>
       <c r="L25">
-        <v>4.8189211201993707E-8</v>
+        <v>0.63664385477890006</v>
       </c>
       <c r="M25">
-        <v>4.8596947009301608E-8</v>
+        <v>0.64203058947783087</v>
       </c>
       <c r="N25">
-        <v>4.9008132727583653E-8</v>
+        <v>0.64746290210938284</v>
       </c>
       <c r="O25">
-        <v>4.9422797547029948E-8</v>
+        <v>0.65294117831496157</v>
       </c>
       <c r="P25">
-        <v>4.9840970904812989E-8</v>
+        <v>0.65846580699893986</v>
       </c>
       <c r="Q25">
-        <v>5.0262682487177348E-8</v>
+        <v>0.66403718035626613</v>
       </c>
       <c r="R25">
-        <v>5.0687962231547208E-8</v>
+        <v>0.66965569390030655</v>
       </c>
       <c r="S25">
-        <v>5.1116840328651598E-8</v>
+        <v>0.67532174649092203</v>
       </c>
       <c r="T25">
-        <v>5.1549347224667557E-8</v>
+        <v>0.68103574036278391</v>
       </c>
       <c r="U25">
-        <v>5.1985513623381627E-8</v>
+        <v>0.68679808115392904</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>0.32195075823137759</v>
+        <v>0.31432914046121552</v>
       </c>
       <c r="B26">
-        <v>4.6869211029142207E-8</v>
+        <v>0.60908647602879595</v>
       </c>
       <c r="C26">
-        <v>4.7265778126220168E-8</v>
+        <v>0.6142400438052622</v>
       </c>
       <c r="D26">
-        <v>4.7665700634217847E-8</v>
+        <v>0.61943721665567442</v>
       </c>
       <c r="E26">
-        <v>4.8069006943746839E-8</v>
+        <v>0.6246783635287988</v>
       </c>
       <c r="F26">
-        <v>4.8475725685635827E-8</v>
+        <v>0.6299638564951302</v>
       </c>
       <c r="G26">
-        <v>4.8885885732963012E-8</v>
+        <v>0.6352940707733048</v>
       </c>
       <c r="H26">
-        <v>4.9299516203105811E-8</v>
+        <v>0.64066938475673763</v>
       </c>
       <c r="I26">
-        <v>4.9716646459807972E-8</v>
+        <v>0.64609018004048435</v>
       </c>
       <c r="J26">
-        <v>5.0137306115264051E-8</v>
+        <v>0.65155684144833104</v>
       </c>
       <c r="K26">
-        <v>5.056152503222164E-8</v>
+        <v>0.65706975706011272</v>
       </c>
       <c r="L26">
-        <v>5.098933332610131E-8</v>
+        <v>0.66262931823926396</v>
       </c>
       <c r="M26">
-        <v>5.1420761367134468E-8</v>
+        <v>0.66823591966060025</v>
       </c>
       <c r="N26">
-        <v>5.1855839782519447E-8</v>
+        <v>0.67388995933833784</v>
       </c>
       <c r="O26">
-        <v>5.2294599458595662E-8</v>
+        <v>0.67959183865434825</v>
       </c>
       <c r="P26">
-        <v>5.2737071543036261E-8</v>
+        <v>0.68534196238665235</v>
       </c>
       <c r="Q26">
-        <v>5.3183287447059281E-8</v>
+        <v>0.69114073873815518</v>
       </c>
       <c r="R26">
-        <v>5.3633278847657618E-8</v>
+        <v>0.69698857936562564</v>
       </c>
       <c r="S26">
-        <v>5.4087077689847741E-8</v>
+        <v>0.70288589940891943</v>
       </c>
       <c r="T26">
-        <v>5.4544716188937388E-8</v>
+        <v>0.7088331175204492</v>
       </c>
       <c r="U26">
-        <v>5.5006226832812729E-8</v>
+        <v>0.71483065589490624</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>0.331597222472232</v>
+        <v>0.32433962264150912</v>
       </c>
       <c r="B27">
-        <v>4.917214031493709E-8</v>
+        <v>0.63745079721641085</v>
       </c>
       <c r="C27">
-        <v>4.958819282603399E-8</v>
+        <v>0.64284435957070274</v>
       </c>
       <c r="D27">
-        <v>5.0007765616925133E-8</v>
+        <v>0.64828355762738421</v>
       </c>
       <c r="E27">
-        <v>5.0430888473201263E-8</v>
+        <v>0.65376877751665885</v>
       </c>
       <c r="F27">
-        <v>5.0857591432473288E-8</v>
+        <v>0.65930040863583417</v>
       </c>
       <c r="G27">
-        <v>5.1287904786504633E-8</v>
+        <v>0.66487884367696293</v>
       </c>
       <c r="H27">
-        <v>5.1721859083361657E-8</v>
+        <v>0.6705044786547224</v>
       </c>
       <c r="I27">
-        <v>5.2159485129582313E-8</v>
+        <v>0.67617771293452611</v>
       </c>
       <c r="J27">
-        <v>5.2600813992362988E-8</v>
+        <v>0.68189894926087513</v>
       </c>
       <c r="K27">
-        <v>5.3045877001764179E-8</v>
+        <v>0.68766859378595069</v>
       </c>
       <c r="L27">
-        <v>5.3494705752934428E-8</v>
+        <v>0.69348705609844474</v>
       </c>
       <c r="M27">
-        <v>5.3947332108353368E-8</v>
+        <v>0.6993547492526373</v>
       </c>
       <c r="N27">
-        <v>5.4403788200093601E-8</v>
+        <v>0.7052720897977206</v>
       </c>
       <c r="O27">
-        <v>5.4864106432101842E-8</v>
+        <v>0.71123949780736861</v>
       </c>
       <c r="P27">
-        <v>5.5328319482499199E-8</v>
+        <v>0.71725739690955947</v>
       </c>
       <c r="Q27">
-        <v>5.5796460305901019E-8</v>
+        <v>0.72332621431664701</v>
       </c>
       <c r="R27">
-        <v>5.6268562135756417E-8</v>
+        <v>0.72944638085569091</v>
       </c>
       <c r="S27">
-        <v>5.6744658486707447E-8</v>
+        <v>0.73561833099903995</v>
       </c>
       <c r="T27">
-        <v>5.7224783156968313E-8</v>
+        <v>0.74184250289517517</v>
       </c>
       <c r="U27">
-        <v>5.7708970230724781E-8</v>
+        <v>0.74811933839981548</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>0.34244949578169542</v>
+        <v>0.32934486373165522</v>
       </c>
       <c r="B28">
-        <v>5.1610536029308143E-8</v>
+        <v>0.66432225939415179</v>
       </c>
       <c r="C28">
-        <v>5.2047220155248613E-8</v>
+        <v>0.66994318503269956</v>
       </c>
       <c r="D28">
-        <v>5.2487599128026953E-8</v>
+        <v>0.67561167012689927</v>
       </c>
       <c r="E28">
-        <v>5.2931704210270627E-8</v>
+        <v>0.6813281170841059</v>
       </c>
       <c r="F28">
-        <v>5.3379566929124687E-8</v>
+        <v>0.68709293171650154</v>
       </c>
       <c r="G28">
-        <v>5.3831219078489872E-8</v>
+        <v>0.69290652326990287</v>
       </c>
       <c r="H28">
-        <v>5.428669272127962E-8</v>
+        <v>0.69876930445281371</v>
       </c>
       <c r="I28">
-        <v>5.47460201916963E-8</v>
+        <v>0.70468169146572379</v>
       </c>
       <c r="J28">
-        <v>5.520923409752657E-8</v>
+        <v>0.71064410403065448</v>
       </c>
       <c r="K28">
-        <v>5.5676367322456268E-8</v>
+        <v>0.71665696542095558</v>
       </c>
       <c r="L28">
-        <v>5.6147453028404789E-8</v>
+        <v>0.72272070249135323</v>
       </c>
       <c r="M28">
-        <v>5.6622524657879231E-8</v>
+        <v>0.72883574570825194</v>
       </c>
       <c r="N28">
-        <v>5.7101615936348558E-8</v>
+        <v>0.73500252918029418</v>
       </c>
       <c r="O28">
-        <v>5.758476087463777E-8</v>
+        <v>0.74122149068917809</v>
       </c>
       <c r="P28">
-        <v>5.8071993771342288E-8</v>
+        <v>0.74749307172073531</v>
       </c>
       <c r="Q28">
-        <v>5.8563349215262837E-8</v>
+        <v>0.75381771749627136</v>
       </c>
       <c r="R28">
-        <v>5.9058862087861009E-8</v>
+        <v>0.76019587700417435</v>
       </c>
       <c r="S28">
-        <v>5.9558567565735359E-8</v>
+        <v>0.76662800303178646</v>
       </c>
       <c r="T28">
-        <v>6.0062501123118677E-8</v>
+        <v>0.77311455219754788</v>
       </c>
       <c r="U28">
-        <v>6.0570698534396352E-8</v>
+        <v>0.77965598498341426</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>0.35089015233861032</v>
+        <v>0.33735324947589002</v>
       </c>
       <c r="B29">
-        <v>5.3777998886526857E-8</v>
+        <v>0.68372942652252033</v>
       </c>
       <c r="C29">
-        <v>5.4233022225661608E-8</v>
+        <v>0.68951455897747527</v>
       </c>
       <c r="D29">
-        <v>5.4691895582339691E-8</v>
+        <v>0.69534864026543797</v>
       </c>
       <c r="E29">
-        <v>5.5154651532110079E-8</v>
+        <v>0.70123208454948438</v>
       </c>
       <c r="F29">
-        <v>5.5621322926148183E-8</v>
+        <v>0.70716530949698386</v>
       </c>
       <c r="G29">
-        <v>5.6091942893587868E-8</v>
+        <v>0.71314873630924847</v>
       </c>
       <c r="H29">
-        <v>5.6566544843873362E-8</v>
+        <v>0.71918278975143535</v>
       </c>
       <c r="I29">
-        <v>5.7045162469130962E-8</v>
+        <v>0.72526789818270021</v>
       </c>
       <c r="J29">
-        <v>5.7527829746560869E-8</v>
+        <v>0.73140449358660631</v>
       </c>
       <c r="K29">
-        <v>5.8014580940849243E-8</v>
+        <v>0.7375930116017928</v>
       </c>
       <c r="L29">
-        <v>5.8505450606600671E-8</v>
+        <v>0.74383389155289859</v>
       </c>
       <c r="M29">
-        <v>5.9000473590791122E-8</v>
+        <v>0.75012757648175166</v>
       </c>
       <c r="N29">
-        <v>5.949968503524187E-8</v>
+        <v>0.75647451317881986</v>
       </c>
       <c r="O29">
-        <v>6.0003120379114156E-8</v>
+        <v>0.76287515221492952</v>
       </c>
       <c r="P29">
-        <v>6.051081536142505E-8</v>
+        <v>0.76932994797325138</v>
       </c>
       <c r="Q29">
-        <v>6.1022806023584482E-8</v>
+        <v>0.77583935868155596</v>
       </c>
       <c r="R29">
-        <v>6.153912871195399E-8</v>
+        <v>0.78240384644474592</v>
       </c>
       <c r="S29">
-        <v>6.2059820080426834E-8</v>
+        <v>0.78902387727765899</v>
       </c>
       <c r="T29">
-        <v>6.2584917093030123E-8</v>
+        <v>0.79569992113815058</v>
       </c>
       <c r="U29">
-        <v>6.3114457026548867E-8</v>
+        <v>0.80243245196045787</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>0.36174242426340408</v>
+        <v>0.34436058700209621</v>
       </c>
       <c r="B30">
-        <v>5.6758260315202507E-8</v>
+        <v>0.71657232473975996</v>
       </c>
       <c r="C30">
-        <v>5.7238500072479418E-8</v>
+        <v>0.72263534565324972</v>
       </c>
       <c r="D30">
-        <v>5.7722803207019637E-8</v>
+        <v>0.72874966665373464</v>
       </c>
       <c r="E30">
-        <v>5.8211204099639248E-8</v>
+        <v>0.73491572179858689</v>
       </c>
       <c r="F30">
-        <v>5.8703737422055388E-8</v>
+        <v>0.74113394881780026</v>
       </c>
       <c r="G30">
-        <v>5.9200438139347542E-8</v>
+        <v>0.74740478914506459</v>
       </c>
       <c r="H30">
-        <v>5.9701341512439692E-8</v>
+        <v>0.75372868794910319</v>
       </c>
       <c r="I30">
-        <v>6.0206483100603554E-8</v>
+        <v>0.76010609416527586</v>
       </c>
       <c r="J30">
-        <v>6.0715898763982955E-8</v>
+        <v>0.76653746052744831</v>
       </c>
       <c r="K30">
-        <v>6.1229624666139518E-8</v>
+        <v>0.77302324360013275</v>
       </c>
       <c r="L30">
-        <v>6.1747697276619921E-8</v>
+        <v>0.7795639038108988</v>
       </c>
       <c r="M30">
-        <v>6.2270153373544892E-8</v>
+        <v>0.78615990548305903</v>
       </c>
       <c r="N30">
-        <v>6.2797030046220093E-8</v>
+        <v>0.79281171686863272</v>
       </c>
       <c r="O30">
-        <v>6.3328364697769125E-8</v>
+        <v>0.79951981018158624</v>
       </c>
       <c r="P30">
-        <v>6.3864195047788766E-8</v>
+        <v>0.8062846616313557</v>
       </c>
       <c r="Q30">
-        <v>6.4404559135026649E-8</v>
+        <v>0.81310675145665312</v>
       </c>
       <c r="R30">
-        <v>6.494949532008175E-8</v>
+        <v>0.8199865639595596</v>
       </c>
       <c r="S30">
-        <v>6.5499042288127551E-8</v>
+        <v>0.82692458753990516</v>
       </c>
       <c r="T30">
-        <v>6.6053239051658286E-8</v>
+        <v>0.83392131472994024</v>
       </c>
       <c r="U30">
-        <v>6.6612124953258503E-8</v>
+        <v>0.84097724222930159</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>0.3738005052568068</v>
+        <v>0.35437106918238981</v>
       </c>
       <c r="B31">
-        <v>5.9738521743877741E-8</v>
+        <v>0.73896520988787695</v>
       </c>
       <c r="C31">
-        <v>6.0243977919296785E-8</v>
+        <v>0.74521770020491329</v>
       </c>
       <c r="D31">
-        <v>6.0753710831699132E-8</v>
+        <v>0.75152309373666359</v>
       </c>
       <c r="E31">
-        <v>6.1267756667167981E-8</v>
+        <v>0.75788183810479226</v>
       </c>
       <c r="F31">
-        <v>6.1786151917962176E-8</v>
+        <v>0.76429438471835609</v>
       </c>
       <c r="G31">
-        <v>6.230893338510676E-8</v>
+        <v>0.77076118880584732</v>
       </c>
       <c r="H31">
-        <v>6.2836138181005559E-8</v>
+        <v>0.77728270944751221</v>
       </c>
       <c r="I31">
-        <v>6.3367803732075689E-8</v>
+        <v>0.78385940960794032</v>
       </c>
       <c r="J31">
-        <v>6.390396778140457E-8</v>
+        <v>0.79049175616893064</v>
       </c>
       <c r="K31">
-        <v>6.444466839142931E-8</v>
+        <v>0.79718021996263644</v>
       </c>
       <c r="L31">
-        <v>6.4989943946638708E-8</v>
+        <v>0.80392527580498896</v>
       </c>
       <c r="M31">
-        <v>6.5539833156298192E-8</v>
+        <v>0.81072740252940423</v>
       </c>
       <c r="N31">
-        <v>6.6094375057197839E-8</v>
+        <v>0.81758708302077709</v>
       </c>
       <c r="O31">
-        <v>6.6653609016423605E-8</v>
+        <v>0.82450480424976036</v>
       </c>
       <c r="P31">
-        <v>6.7217574734152006E-8</v>
+        <v>0.83148105730733524</v>
       </c>
       <c r="Q31">
-        <v>6.7786312246468326E-8</v>
+        <v>0.83851633743967313</v>
       </c>
       <c r="R31">
-        <v>6.8359861928209035E-8</v>
+        <v>0.84561114408329541</v>
       </c>
       <c r="S31">
-        <v>6.8938264495827765E-8</v>
+        <v>0.85276598090052669</v>
       </c>
       <c r="T31">
-        <v>6.9521561010285932E-8</v>
+        <v>0.85998135581525037</v>
       </c>
       <c r="U31">
-        <v>7.0109792879967623E-8</v>
+        <v>0.86725778104896678</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>0.3810353541297824</v>
+        <v>0.3613784067085945</v>
       </c>
       <c r="B32">
-        <v>6.1770518172520272E-8</v>
+        <v>0.76882239008536435</v>
       </c>
       <c r="C32">
-        <v>6.2293167360308954E-8</v>
+        <v>0.77532750627379599</v>
       </c>
       <c r="D32">
-        <v>6.282023875761731E-8</v>
+        <v>0.78188766318056635</v>
       </c>
       <c r="E32">
-        <v>6.3351769781392453E-8</v>
+        <v>0.78850332651306387</v>
       </c>
       <c r="F32">
-        <v>6.3887798165171667E-8</v>
+        <v>0.79517496591909487</v>
       </c>
       <c r="G32">
-        <v>6.442836196176111E-8</v>
+        <v>0.80190305502022208</v>
       </c>
       <c r="H32">
-        <v>6.4973499545937172E-8</v>
+        <v>0.80868807144538868</v>
       </c>
       <c r="I32">
-        <v>6.5523249617170679E-8</v>
+        <v>0.81553049686482382</v>
       </c>
       <c r="J32">
-        <v>6.6077651202374219E-8</v>
+        <v>0.82243081702423804</v>
       </c>
       <c r="K32">
-        <v>6.6636743658672709E-8</v>
+        <v>0.82938952177930558</v>
       </c>
       <c r="L32">
-        <v>6.7200566676197329E-8</v>
+        <v>0.83640710513044003</v>
       </c>
       <c r="M32">
-        <v>6.7769160280903072E-8</v>
+        <v>0.84348406525786201</v>
       </c>
       <c r="N32">
-        <v>6.8342564837410294E-8</v>
+        <v>0.85062090455696704</v>
       </c>
       <c r="O32">
-        <v>6.8920821051870218E-8</v>
+        <v>0.85781812967399007</v>
       </c>
       <c r="P32">
-        <v>6.9503969974854565E-8</v>
+        <v>0.86507625154197187</v>
       </c>
       <c r="Q32">
-        <v>7.0092053004269837E-8</v>
+        <v>0.87239578541703056</v>
       </c>
       <c r="R32">
-        <v>7.0685111888296177E-8</v>
+        <v>0.87977725091494063</v>
       </c>
       <c r="S32">
-        <v>7.1283188728351029E-8</v>
+        <v>0.88722117204801965</v>
       </c>
       <c r="T32">
-        <v>7.1886325982077899E-8</v>
+        <v>0.89472807726232806</v>
       </c>
       <c r="U32">
-        <v>7.2494566466360593E-8</v>
+        <v>0.90229849947518448</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>0.39429924280712447</v>
+        <v>0.3693867924528294</v>
       </c>
       <c r="B33">
-        <v>6.4615313172619833E-8</v>
+        <v>0.79121527523348367</v>
       </c>
       <c r="C33">
-        <v>6.5162032577726017E-8</v>
+        <v>0.79790986082546178</v>
       </c>
       <c r="D33">
-        <v>6.5713377853902787E-8</v>
+        <v>0.80466109026349741</v>
       </c>
       <c r="E33">
-        <v>6.6269388141306722E-8</v>
+        <v>0.81146944281927158</v>
       </c>
       <c r="F33">
-        <v>6.6830102911265E-8</v>
+        <v>0.81833540181965303</v>
       </c>
       <c r="G33">
-        <v>6.7395561969077239E-8</v>
+        <v>0.82525945468100725</v>
       </c>
       <c r="H33">
-        <v>6.7965805456841458E-8</v>
+        <v>0.83224209294380003</v>
       </c>
       <c r="I33">
-        <v>6.8540873856303677E-8</v>
+        <v>0.83928381230749072</v>
       </c>
       <c r="J33">
-        <v>6.9120807991731733E-8</v>
+        <v>0.84638511266572281</v>
       </c>
       <c r="K33">
-        <v>6.9705649032813487E-8</v>
+        <v>0.85354649814181172</v>
       </c>
       <c r="L33">
-        <v>7.0295438497579429E-8</v>
+        <v>0.86076847712453253</v>
       </c>
       <c r="M33">
-        <v>7.0890218255349932E-8</v>
+        <v>0.86805156230420966</v>
       </c>
       <c r="N33">
-        <v>7.1490030529707767E-8</v>
+        <v>0.87539627070911374</v>
       </c>
       <c r="O33">
-        <v>7.2094917901495486E-8</v>
+        <v>0.88280312374216663</v>
       </c>
       <c r="P33">
-        <v>7.2704923311838197E-8</v>
+        <v>0.89027264721795374</v>
       </c>
       <c r="Q33">
-        <v>7.3320090065191976E-8</v>
+        <v>0.8978053714000529</v>
       </c>
       <c r="R33">
-        <v>7.3940461832418218E-8</v>
+        <v>0.90540183103867888</v>
       </c>
       <c r="S33">
-        <v>7.4566082653883601E-8</v>
+        <v>0.91306256540864383</v>
       </c>
       <c r="T33">
-        <v>7.5196996942586675E-8</v>
+        <v>0.92078811834764085</v>
       </c>
       <c r="U33">
-        <v>7.5833249487310765E-8</v>
+        <v>0.92857903829485222</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>0.40756313148446671</v>
+        <v>0.37439203354297679</v>
       </c>
       <c r="B34">
-        <v>6.7866507458447894E-8</v>
+        <v>0.8091295833519746</v>
       </c>
       <c r="C34">
-        <v>6.8440735683345513E-8</v>
+        <v>0.81597574446679</v>
       </c>
       <c r="D34">
-        <v>6.9019822535371881E-8</v>
+        <v>0.82287983192983771</v>
       </c>
       <c r="E34">
-        <v>6.9603809124065896E-8</v>
+        <v>0.82984233586423317</v>
       </c>
       <c r="F34">
-        <v>7.0192736906800221E-8</v>
+        <v>0.83686375054009488</v>
       </c>
       <c r="G34">
-        <v>7.0786647691724229E-8</v>
+        <v>0.84394457440963078</v>
       </c>
       <c r="H34">
-        <v>7.1385583640732075E-8</v>
+        <v>0.85108531014252453</v>
       </c>
       <c r="I34">
-        <v>7.198958727245566E-8</v>
+        <v>0.8582864646616194</v>
       </c>
       <c r="J34">
-        <v>7.2598701465283166E-8</v>
+        <v>0.86554854917890578</v>
       </c>
       <c r="K34">
-        <v>7.3212969460402947E-8</v>
+        <v>0.87287207923181187</v>
       </c>
       <c r="L34">
-        <v>7.383243486487323E-8</v>
+        <v>0.88025757471980182</v>
       </c>
       <c r="M34">
-        <v>7.4457141654717754E-8</v>
+        <v>0.88770555994128275</v>
       </c>
       <c r="N34">
-        <v>7.5087134178047727E-8</v>
+        <v>0.89521656363082625</v>
       </c>
       <c r="O34">
-        <v>7.5722457158210069E-8</v>
+        <v>0.90279111899670295</v>
       </c>
       <c r="P34">
-        <v>7.6363155696962333E-8</v>
+        <v>0.91042976375873419</v>
       </c>
       <c r="Q34">
-        <v>7.7009275277674423E-8</v>
+        <v>0.91813304018646591</v>
       </c>
       <c r="R34">
-        <v>7.7660861768557669E-8</v>
+        <v>0.92590149513766451</v>
       </c>
       <c r="S34">
-        <v>7.8317961425920821E-8</v>
+        <v>0.93373568009713792</v>
       </c>
       <c r="T34">
-        <v>7.8980620897453823E-8</v>
+        <v>0.94163615121588573</v>
       </c>
       <c r="U34">
-        <v>7.9648887225539543E-8</v>
+        <v>0.94960346935058126</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>0.41720959572532101</v>
+        <v>0.38640461215932909</v>
       </c>
       <c r="B35">
-        <v>7.0033970315667157E-8</v>
+        <v>0.84495819958896423</v>
       </c>
       <c r="C35">
-        <v>7.0626537753759084E-8</v>
+        <v>0.85210751174945409</v>
       </c>
       <c r="D35">
-        <v>7.1224118989685188E-8</v>
+        <v>0.85931731526252608</v>
       </c>
       <c r="E35">
-        <v>7.1826756445905924E-8</v>
+        <v>0.86658812195416413</v>
       </c>
       <c r="F35">
-        <v>7.243449290382428E-8</v>
+        <v>0.87392044798098656</v>
       </c>
       <c r="G35">
-        <v>7.3047371506822814E-8</v>
+        <v>0.88131481386688559</v>
       </c>
       <c r="H35">
-        <v>7.3665435763326406E-8</v>
+        <v>0.8887717445399812</v>
       </c>
       <c r="I35">
-        <v>7.4288729549890938E-8</v>
+        <v>0.89629176936988486</v>
       </c>
       <c r="J35">
-        <v>7.4917297114318068E-8</v>
+        <v>0.90387542220527994</v>
       </c>
       <c r="K35">
-        <v>7.5551183078796538E-8</v>
+        <v>0.91152324141182017</v>
       </c>
       <c r="L35">
-        <v>7.6190432443069728E-8</v>
+        <v>0.9192357699103485</v>
       </c>
       <c r="M35">
-        <v>7.6835090587630254E-8</v>
+        <v>0.92701355521543749</v>
       </c>
       <c r="N35">
-        <v>7.7485203276941661E-8</v>
+        <v>0.9348571494742598</v>
       </c>
       <c r="O35">
-        <v>7.8140816662687084E-8</v>
+        <v>0.94276710950578402</v>
       </c>
       <c r="P35">
-        <v>7.8801977287045717E-8</v>
+        <v>0.95074399684030386</v>
       </c>
       <c r="Q35">
-        <v>7.946873208599669E-8</v>
+        <v>0.95878837775930037</v>
       </c>
       <c r="R35">
-        <v>8.0141128392651298E-8</v>
+        <v>0.96690082333564431</v>
       </c>
       <c r="S35">
-        <v>8.0819213940612944E-8</v>
+        <v>0.97508190947413509</v>
       </c>
       <c r="T35">
-        <v>8.1503036867365944E-8</v>
+        <v>0.9833322169523846</v>
       </c>
       <c r="U35">
-        <v>8.219264571769272E-8</v>
+        <v>0.99165233146204823</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>0.42926767671872379</v>
+        <v>0.39541404612159259</v>
       </c>
       <c r="B36">
-        <v>7.2607832458614379E-8</v>
+        <v>0.88078681582595364</v>
       </c>
       <c r="C36">
-        <v>7.322217771237452E-8</v>
+        <v>0.88823927903211808</v>
       </c>
       <c r="D36">
-        <v>7.3841721029181556E-8</v>
+        <v>0.89575479859521423</v>
       </c>
       <c r="E36">
-        <v>7.4466506390590261E-8</v>
+        <v>0.90333390804409508</v>
       </c>
       <c r="F36">
-        <v>7.5096578150289657E-8</v>
+        <v>0.91097714542187813</v>
       </c>
       <c r="G36">
-        <v>7.5731981037251679E-8</v>
+        <v>0.91868505332414041</v>
       </c>
       <c r="H36">
-        <v>7.6372760158906459E-8</v>
+        <v>0.92645817893743798</v>
       </c>
       <c r="I36">
-        <v>7.7018961004344591E-8</v>
+        <v>0.93429707407815032</v>
       </c>
       <c r="J36">
-        <v>7.7670629447546307E-8</v>
+        <v>0.94220229523165389</v>
       </c>
       <c r="K36">
-        <v>7.8327811750638177E-8</v>
+        <v>0.95017440359182848</v>
       </c>
       <c r="L36">
-        <v>7.8990554567177317E-8</v>
+        <v>0.95821396510089496</v>
       </c>
       <c r="M36">
-        <v>7.965890494546312E-8</v>
+        <v>0.96632155048959201</v>
       </c>
       <c r="N36">
-        <v>8.0332910331877461E-8</v>
+        <v>0.9744977353176929</v>
       </c>
       <c r="O36">
-        <v>8.1012618574252805E-8</v>
+        <v>0.98274310001486498</v>
       </c>
       <c r="P36">
-        <v>8.1698077925268996E-8</v>
+        <v>0.99105822992187331</v>
       </c>
       <c r="Q36">
-        <v>8.2389337045878642E-8</v>
+        <v>0.99944371533213472</v>
       </c>
       <c r="R36">
-        <v>8.3086445008761702E-8</v>
+        <v>1.0079001515336239</v>
       </c>
       <c r="S36">
-        <v>8.3789451301809094E-8</v>
+        <v>1.016428138851132</v>
       </c>
       <c r="T36">
-        <v>8.4498405831635774E-8</v>
+        <v>1.025028282688883</v>
       </c>
       <c r="U36">
-        <v>8.5213358927123815E-8</v>
+        <v>1.033701193573515</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>0.44011995002818721</v>
+        <v>0.40542452830188619</v>
       </c>
       <c r="B37">
-        <v>7.4504362458680206E-8</v>
+        <v>0.90616541899381775</v>
       </c>
       <c r="C37">
-        <v>7.513475452398534E-8</v>
+        <v>0.9138326141906683</v>
       </c>
       <c r="D37">
-        <v>7.5770480426704643E-8</v>
+        <v>0.92156468262253155</v>
       </c>
       <c r="E37">
-        <v>7.6411585297199217E-8</v>
+        <v>0.92936217319112591</v>
       </c>
       <c r="F37">
-        <v>7.7058114647684634E-8</v>
+        <v>0.93722563944250592</v>
       </c>
       <c r="G37">
-        <v>7.7710114375461848E-8</v>
+        <v>0.94515563960635884</v>
       </c>
       <c r="H37">
-        <v>7.8367630766175419E-8</v>
+        <v>0.95315273663563271</v>
       </c>
       <c r="I37">
-        <v>7.9030710497099346E-8</v>
+        <v>0.96121749824650105</v>
       </c>
       <c r="J37">
-        <v>7.9699400640450717E-8</v>
+        <v>0.96935049695866493</v>
       </c>
       <c r="K37">
-        <v>8.0373748666731438E-8</v>
+        <v>0.97755231013599708</v>
       </c>
       <c r="L37">
-        <v>8.1053802448098126E-8</v>
+        <v>0.98582352002752827</v>
       </c>
       <c r="M37">
-        <v>8.1739610261760422E-8</v>
+        <v>0.99416471380878102</v>
       </c>
       <c r="N37">
-        <v>8.2431220793408492E-8</v>
+        <v>1.0025764836234541</v>
       </c>
       <c r="O37">
-        <v>8.3128683140669029E-8</v>
+        <v>1.01105942662546</v>
       </c>
       <c r="P37">
-        <v>8.3832046816590782E-8</v>
+        <v>1.0196141450213141</v>
       </c>
       <c r="Q37">
-        <v>8.4541361753159424E-8</v>
+        <v>1.028241246112888</v>
       </c>
       <c r="R37">
-        <v>8.5256678304842423E-8</v>
+        <v>1.036941342340522</v>
       </c>
       <c r="S37">
-        <v>8.5978047252163498E-8</v>
+        <v>1.045715051326501</v>
       </c>
       <c r="T37">
-        <v>8.6705519805307652E-8</v>
+        <v>1.0545629959188989</v>
       </c>
       <c r="U37">
-        <v>8.7439147607756632E-8</v>
+        <v>1.0634858042358</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>0.44856060658510222</v>
+        <v>0.41143081761006223</v>
       </c>
       <c r="B38">
-        <v>7.6129959601594236E-8</v>
+        <v>0.93602259919131026</v>
       </c>
       <c r="C38">
-        <v>7.6774106076795075E-8</v>
+        <v>0.94394242025955633</v>
       </c>
       <c r="D38">
-        <v>7.742370276743919E-8</v>
+        <v>0.95192925206643975</v>
       </c>
       <c r="E38">
-        <v>7.8078795788578785E-8</v>
+        <v>0.95998366159940285</v>
       </c>
       <c r="F38">
-        <v>7.8739431645452238E-8</v>
+        <v>0.96810622064325036</v>
       </c>
       <c r="G38">
-        <v>7.9405657236785337E-8</v>
+        <v>0.97629750582073926</v>
       </c>
       <c r="H38">
-        <v>8.0077519858120714E-8</v>
+        <v>0.98455809863351473</v>
       </c>
       <c r="I38">
-        <v>8.0755067205175324E-8</v>
+        <v>0.99288858550339043</v>
       </c>
       <c r="J38">
-        <v>8.143834737722642E-8</v>
+        <v>1.001289557813978</v>
       </c>
       <c r="K38">
-        <v>8.2127408880526168E-8</v>
+        <v>1.009761611952672</v>
       </c>
       <c r="L38">
-        <v>8.2822300631745007E-8</v>
+        <v>1.018305349352985</v>
       </c>
       <c r="M38">
-        <v>8.352307196144434E-8</v>
+        <v>1.0269213765372449</v>
       </c>
       <c r="N38">
-        <v>8.4229772617578459E-8</v>
+        <v>1.0356103051596499</v>
       </c>
       <c r="O38">
-        <v>8.4942452769026314E-8</v>
+        <v>1.0443727520496959</v>
       </c>
       <c r="P38">
-        <v>8.566116300915285E-8</v>
+        <v>1.0532093392559569</v>
       </c>
       <c r="Q38">
-        <v>8.6385954359400654E-8</v>
+        <v>1.0621206940902519</v>
       </c>
       <c r="R38">
-        <v>8.7116878272912142E-8</v>
+        <v>1.071107449172173</v>
       </c>
       <c r="S38">
-        <v>8.7853986638182101E-8</v>
+        <v>1.0801702424740001</v>
       </c>
       <c r="T38">
-        <v>8.8597331782741233E-8</v>
+        <v>1.0893097173659829</v>
       </c>
       <c r="U38">
-        <v>8.9346966476871008E-8</v>
+        <v>1.098526522662024</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>0.45820707082595652</v>
+        <v>0.42344339622641453</v>
       </c>
       <c r="B39">
-        <v>7.7755556744508267E-8</v>
+        <v>0.95542976631967735</v>
       </c>
       <c r="C39">
-        <v>7.8413457629604836E-8</v>
+        <v>0.96351379420433036</v>
       </c>
       <c r="D39">
-        <v>7.907692510817375E-8</v>
+        <v>0.971666222204977</v>
       </c>
       <c r="E39">
-        <v>7.9746006279958378E-8</v>
+        <v>0.97988762906477989</v>
       </c>
       <c r="F39">
-        <v>8.0420748643219868E-8</v>
+        <v>0.98817859842373101</v>
       </c>
       <c r="G39">
-        <v>8.1101200098108826E-8</v>
+        <v>0.99653971886008319</v>
       </c>
       <c r="H39">
-        <v>8.1787408950066022E-8</v>
+        <v>1.0049715839321349</v>
       </c>
       <c r="I39">
-        <v>8.2479423913251329E-8</v>
+        <v>1.0134747922203651</v>
       </c>
       <c r="J39">
-        <v>8.317729411400215E-8</v>
+        <v>1.022049947369928</v>
       </c>
       <c r="K39">
-        <v>8.3881069094320885E-8</v>
+        <v>1.030697658133507</v>
       </c>
       <c r="L39">
-        <v>8.4590798815391914E-8</v>
+        <v>1.0394185384145289</v>
       </c>
       <c r="M39">
-        <v>8.5306533661128245E-8</v>
+        <v>1.048213207310742</v>
       </c>
       <c r="N39">
-        <v>8.6028324441748439E-8</v>
+        <v>1.0570822891581739</v>
       </c>
       <c r="O39">
-        <v>8.6756222397383612E-8</v>
+        <v>1.0660264135754449</v>
       </c>
       <c r="P39">
-        <v>8.7490279201714918E-8</v>
+        <v>1.075046215508471</v>
       </c>
       <c r="Q39">
-        <v>8.8230546965641871E-8</v>
+        <v>1.0841423352755351</v>
       </c>
       <c r="R39">
-        <v>8.8977078240981888E-8</v>
+        <v>1.093315418612743</v>
       </c>
       <c r="S39">
-        <v>8.9729926024200717E-8</v>
+        <v>1.102566116719871</v>
       </c>
       <c r="T39">
-        <v>9.04891437601748E-8</v>
+        <v>1.111895086306584</v>
       </c>
       <c r="U39">
-        <v>9.1254785345985397E-8</v>
+        <v>1.1213029896390661</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>0.46664772738287152</v>
+        <v>0.43545597484276671</v>
       </c>
       <c r="B40">
-        <v>7.8839288173118177E-8</v>
+        <v>0.99125838255666698</v>
       </c>
       <c r="C40">
-        <v>7.9506358664811887E-8</v>
+        <v>0.99964556148699446</v>
       </c>
       <c r="D40">
-        <v>8.0179073335330662E-8</v>
+        <v>1.0081037055376649</v>
       </c>
       <c r="E40">
-        <v>8.0857479940878663E-8</v>
+        <v>1.016633415154711</v>
       </c>
       <c r="F40">
-        <v>8.1541626641732168E-8</v>
+        <v>1.0252352958646229</v>
       </c>
       <c r="G40">
-        <v>8.2231562005658409E-8</v>
+        <v>1.0339099583173379</v>
       </c>
       <c r="H40">
-        <v>8.2927335011363459E-8</v>
+        <v>1.0426580183295919</v>
       </c>
       <c r="I40">
-        <v>8.3628995051969226E-8</v>
+        <v>1.0514800969286311</v>
       </c>
       <c r="J40">
-        <v>8.4336591938519885E-8</v>
+        <v>1.060376820396302</v>
       </c>
       <c r="K40">
-        <v>8.5050175903517971E-8</v>
+        <v>1.069348820313516</v>
       </c>
       <c r="L40">
-        <v>8.5769797604490447E-8</v>
+        <v>1.078396733605075</v>
       </c>
       <c r="M40">
-        <v>8.6495508127584799E-8</v>
+        <v>1.087521202584897</v>
       </c>
       <c r="N40">
-        <v>8.7227358991195711E-8</v>
+        <v>1.096722875001608</v>
       </c>
       <c r="O40">
-        <v>8.7965402149622411E-8</v>
+        <v>1.106002404084526</v>
       </c>
       <c r="P40">
-        <v>8.8709689996756901E-8</v>
+        <v>1.115360448590041</v>
       </c>
       <c r="Q40">
-        <v>8.9460275369803309E-8</v>
+        <v>1.1247976728483691</v>
       </c>
       <c r="R40">
-        <v>9.0217211553028993E-8</v>
+        <v>1.1343147468107231</v>
       </c>
       <c r="S40">
-        <v>9.0980552281547083E-8</v>
+        <v>1.1439123460968681</v>
       </c>
       <c r="T40">
-        <v>9.1750351745131152E-8</v>
+        <v>1.153591152043083</v>
       </c>
       <c r="U40">
-        <v>9.2526664592062296E-8</v>
+        <v>1.163351851750533</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>0.47870580837627419</v>
+        <v>0.44746855345911901</v>
       </c>
       <c r="B41">
-        <v>8.0193952458879856E-8</v>
+        <v>1.0211155627541519</v>
       </c>
       <c r="C41">
-        <v>8.0872484958820008E-8</v>
+        <v>1.029755367555875</v>
       </c>
       <c r="D41">
-        <v>8.1556758619276127E-8</v>
+        <v>1.0384682749815659</v>
       </c>
       <c r="E41">
-        <v>8.2246822017028312E-8</v>
+        <v>1.0472549035629799</v>
       </c>
       <c r="F41">
-        <v>8.2942724139871829E-8</v>
+        <v>1.0561158770653589</v>
       </c>
       <c r="G41">
-        <v>8.3644514390094661E-8</v>
+        <v>1.06505182453171</v>
       </c>
       <c r="H41">
-        <v>8.4352242587984548E-8</v>
+        <v>1.074063380327466</v>
       </c>
       <c r="I41">
-        <v>8.5065958975365899E-8</v>
+        <v>1.0831511841855119</v>
       </c>
       <c r="J41">
-        <v>8.5785714219166314E-8</v>
+        <v>1.0923158812516069</v>
       </c>
       <c r="K41">
-        <v>8.6511559415013575E-8</v>
+        <v>1.101558122130182</v>
       </c>
       <c r="L41">
-        <v>8.7243546090862883E-8</v>
+        <v>1.110878562930524</v>
       </c>
       <c r="M41">
-        <v>8.7981726210654724E-8</v>
+        <v>1.1202778653133521</v>
       </c>
       <c r="N41">
-        <v>8.8726152178004019E-8</v>
+        <v>1.129756696537795</v>
       </c>
       <c r="O41">
-        <v>8.9476876839920161E-8</v>
+        <v>1.139315729508753</v>
       </c>
       <c r="P41">
-        <v>9.0233953490558629E-8</v>
+        <v>1.148955642824675</v>
       </c>
       <c r="Q41">
-        <v>9.0997435875004325E-8</v>
+        <v>1.158677120825724</v>
       </c>
       <c r="R41">
-        <v>9.1767378193087115E-8</v>
+        <v>1.168480853642365</v>
       </c>
       <c r="S41">
-        <v>9.2543835103229264E-8</v>
+        <v>1.1783675372443581</v>
       </c>
       <c r="T41">
-        <v>9.3326861726325814E-8</v>
+        <v>1.188337873490158</v>
       </c>
       <c r="U41">
-        <v>9.411651364965761E-8</v>
+        <v>1.1983925701767471</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>0.49196969705361637</v>
+        <v>0.45848008385744271</v>
       </c>
       <c r="B42">
-        <v>8.1548616744640992E-8</v>
+        <v>1.03902987087265</v>
       </c>
       <c r="C42">
-        <v>8.2238611252827573E-8</v>
+        <v>1.04782125119721</v>
       </c>
       <c r="D42">
-        <v>8.2934443903221009E-8</v>
+        <v>1.0566870166479141</v>
       </c>
       <c r="E42">
-        <v>8.3636164093177391E-8</v>
+        <v>1.065627796607949</v>
       </c>
       <c r="F42">
-        <v>8.4343821638010934E-8</v>
+        <v>1.0746442257858091</v>
       </c>
       <c r="G42">
-        <v>8.5057466774530303E-8</v>
+        <v>1.083736944260342</v>
       </c>
       <c r="H42">
-        <v>8.5777150164605053E-8</v>
+        <v>1.092906597526198</v>
       </c>
       <c r="I42">
-        <v>8.6502922898761963E-8</v>
+        <v>1.1021538365396479</v>
       </c>
       <c r="J42">
-        <v>8.723483649981216E-8</v>
+        <v>1.1114793177647979</v>
       </c>
       <c r="K42">
-        <v>8.7972942926508584E-8</v>
+        <v>1.120883703220191</v>
       </c>
       <c r="L42">
-        <v>8.8717294577234683E-8</v>
+        <v>1.130367660525802</v>
       </c>
       <c r="M42">
-        <v>8.9467944293724026E-8</v>
+        <v>1.139931862950434</v>
       </c>
       <c r="N42">
-        <v>9.0224945364811705E-8</v>
+        <v>1.149576989459516</v>
       </c>
       <c r="O42">
-        <v>9.0988351530217277E-8</v>
+        <v>1.159303724763298</v>
       </c>
       <c r="P42">
-        <v>9.1758216984359722E-8</v>
+        <v>1.169112759365464</v>
       </c>
       <c r="Q42">
-        <v>9.2534596380204706E-8</v>
+        <v>1.1790047896121449</v>
       </c>
       <c r="R42">
-        <v>9.3317544833144574E-8</v>
+        <v>1.1889805177413599</v>
       </c>
       <c r="S42">
-        <v>9.4107117924910795E-8</v>
+        <v>1.1990406519328609</v>
       </c>
       <c r="T42">
-        <v>9.4903371707519813E-8</v>
+        <v>1.2091859063584121</v>
       </c>
       <c r="U42">
-        <v>9.5706362707252275E-8</v>
+        <v>1.219417001232485</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>0.50282197036307963</v>
+        <v>0.47049266247379501</v>
       </c>
       <c r="B43">
-        <v>8.2090482458946238E-8</v>
+        <v>1.059929897010893</v>
       </c>
       <c r="C43">
-        <v>8.2785061770431383E-8</v>
+        <v>1.06889811544543</v>
       </c>
       <c r="D43">
-        <v>8.3485518016799783E-8</v>
+        <v>1.077942215258648</v>
       </c>
       <c r="E43">
-        <v>8.4191900923637838E-8</v>
+        <v>1.087062838493742</v>
       </c>
       <c r="F43">
-        <v>8.4904260637267389E-8</v>
+        <v>1.096260632626328</v>
       </c>
       <c r="G43">
-        <v>8.5622647728305413E-8</v>
+        <v>1.1055362506104069</v>
       </c>
       <c r="H43">
-        <v>8.6347113195254076E-8</v>
+        <v>1.1148903509247139</v>
       </c>
       <c r="I43">
-        <v>8.7077708468121235E-8</v>
+        <v>1.124323597619469</v>
       </c>
       <c r="J43">
-        <v>8.7814485412071332E-8</v>
+        <v>1.1338366603635159</v>
       </c>
       <c r="K43">
-        <v>8.8557496331107445E-8</v>
+        <v>1.143430214491862</v>
       </c>
       <c r="L43">
-        <v>8.9306793971784274E-8</v>
+        <v>1.15310494105362</v>
       </c>
       <c r="M43">
-        <v>9.0062431526952648E-8</v>
+        <v>1.162861526860357</v>
       </c>
       <c r="N43">
-        <v>9.0824462639535685E-8</v>
+        <v>1.172700664534851</v>
       </c>
       <c r="O43">
-        <v>9.1592941406337007E-8</v>
+        <v>1.182623052560261</v>
       </c>
       <c r="P43">
-        <v>9.2367922381881051E-8</v>
+        <v>1.192629395329712</v>
       </c>
       <c r="Q43">
-        <v>9.3149460582285769E-8</v>
+        <v>1.2027204031962979</v>
       </c>
       <c r="R43">
-        <v>9.3937611489168471E-8</v>
+        <v>1.2128967925235139</v>
       </c>
       <c r="S43">
-        <v>9.4732431053584329E-8</v>
+        <v>1.223159285736108</v>
       </c>
       <c r="T43">
-        <v>9.5533975699998327E-8</v>
+        <v>1.233508611371368</v>
       </c>
       <c r="U43">
-        <v>9.6342302330291088E-8</v>
+        <v>1.24394550413084</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>0.51729166672436122</v>
+        <v>0.48550838574423449</v>
       </c>
       <c r="B44">
-        <v>8.2496881744674752E-8</v>
+        <v>1.0778442051293851</v>
       </c>
       <c r="C44">
-        <v>8.319489965863383E-8</v>
+        <v>1.086963999086759</v>
       </c>
       <c r="D44">
-        <v>8.3898823601983413E-8</v>
+        <v>1.0961609569249879</v>
       </c>
       <c r="E44">
-        <v>8.4608703546482743E-8</v>
+        <v>1.1054357315387029</v>
       </c>
       <c r="F44">
-        <v>8.532458988670929E-8</v>
+        <v>1.11478898134677</v>
       </c>
       <c r="G44">
-        <v>8.6046533443636275E-8</v>
+        <v>1.12422137033903</v>
       </c>
       <c r="H44">
-        <v>8.6774585468240393E-8</v>
+        <v>1.133733568123438</v>
       </c>
       <c r="I44">
-        <v>8.7508797645140233E-8</v>
+        <v>1.1433262499735981</v>
       </c>
       <c r="J44">
-        <v>8.8249222096265251E-8</v>
+        <v>1.1530000968766989</v>
       </c>
       <c r="K44">
-        <v>8.8995911384556114E-8</v>
+        <v>1.1627557955818619</v>
       </c>
       <c r="L44">
-        <v>8.9748918517695988E-8</v>
+        <v>1.1725940386488889</v>
       </c>
       <c r="M44">
-        <v>9.050829695187361E-8</v>
+        <v>1.1825155244974299</v>
       </c>
       <c r="N44">
-        <v>9.127410059557816E-8</v>
+        <v>1.1925209574565641</v>
       </c>
       <c r="O44">
-        <v>9.2046383813426322E-8</v>
+        <v>1.202611047814798</v>
       </c>
       <c r="P44">
-        <v>9.2825201430021555E-8</v>
+        <v>1.212786511870493</v>
       </c>
       <c r="Q44">
-        <v>9.3610608733846063E-8</v>
+        <v>1.223048071982711</v>
       </c>
       <c r="R44">
-        <v>9.4402661481185907E-8</v>
+        <v>1.2333964566225</v>
       </c>
       <c r="S44">
-        <v>9.5201415900088963E-8</v>
+        <v>1.2438324004246031</v>
       </c>
       <c r="T44">
-        <v>9.6006928694356738E-8</v>
+        <v>1.254356644239613</v>
       </c>
       <c r="U44">
-        <v>9.6819257047569669E-8</v>
+        <v>1.26496993518657</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>0.5317613644703123</v>
+        <v>0.5055293501048217</v>
       </c>
       <c r="B45">
-        <v>8.2361415316098563E-8</v>
+        <v>1.0868013591886341</v>
       </c>
       <c r="C45">
-        <v>8.3058287029232997E-8</v>
+        <v>1.0959969409074271</v>
       </c>
       <c r="D45">
-        <v>8.3761055073588838E-8</v>
+        <v>1.1052703277581619</v>
       </c>
       <c r="E45">
-        <v>8.4469769338867757E-8</v>
+        <v>1.114622178061188</v>
       </c>
       <c r="F45">
-        <v>8.5184480136895305E-8</v>
+        <v>1.124053155706995</v>
       </c>
       <c r="G45">
-        <v>8.5905238205192637E-8</v>
+        <v>1.133563930203346</v>
       </c>
       <c r="H45">
-        <v>8.663209471057827E-8</v>
+        <v>1.1431551767228041</v>
       </c>
       <c r="I45">
-        <v>8.7365101252800554E-8</v>
+        <v>1.1528275761506659</v>
       </c>
       <c r="J45">
-        <v>8.8104309868200594E-8</v>
+        <v>1.1625818151332949</v>
       </c>
       <c r="K45">
-        <v>8.8849773033406545E-8</v>
+        <v>1.1724185861268659</v>
       </c>
       <c r="L45">
-        <v>8.9601543669058733E-8</v>
+        <v>1.182338587446528</v>
       </c>
       <c r="M45">
-        <v>9.0359675143566601E-8</v>
+        <v>1.192342523315971</v>
       </c>
       <c r="N45">
-        <v>9.1124221276897317E-8</v>
+        <v>1.202431103917424</v>
       </c>
       <c r="O45">
-        <v>9.1895236344396555E-8</v>
+        <v>1.21260504544207</v>
       </c>
       <c r="P45">
-        <v>9.2672775080641391E-8</v>
+        <v>1.222865070140887</v>
       </c>
       <c r="Q45">
-        <v>9.3456892683325943E-8</v>
+        <v>1.233211906375921</v>
       </c>
       <c r="R45">
-        <v>9.4247644817180069E-8</v>
+        <v>1.243646288671997</v>
       </c>
       <c r="S45">
-        <v>9.5045087617920739E-8</v>
+        <v>1.254168957768854</v>
       </c>
       <c r="T45">
-        <v>9.5849277696237246E-8</v>
+        <v>1.26478066067374</v>
       </c>
       <c r="U45">
-        <v>9.6660272141810111E-8</v>
+        <v>1.275482150714438</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>0.54623106083159401</v>
+        <v>0.51754192872117388</v>
       </c>
       <c r="B46">
-        <v>8.1413150316065385E-8</v>
+        <v>1.0897870772083791</v>
       </c>
       <c r="C46">
-        <v>8.2101998623427309E-8</v>
+        <v>1.0990079215143109</v>
       </c>
       <c r="D46">
-        <v>8.279667537482703E-8</v>
+        <v>1.108306784702549</v>
       </c>
       <c r="E46">
-        <v>8.3497229885563E-8</v>
+        <v>1.1176843269020109</v>
       </c>
       <c r="F46">
-        <v>8.4203711888197545E-8</v>
+        <v>1.1271412138270649</v>
       </c>
       <c r="G46">
-        <v>8.4916171536087274E-8</v>
+        <v>1.136678116824779</v>
       </c>
       <c r="H46">
-        <v>8.5634659406943512E-8</v>
+        <v>1.1462957129225879</v>
       </c>
       <c r="I46">
-        <v>8.6359226506422906E-8</v>
+        <v>1.15599468487635</v>
       </c>
       <c r="J46">
-        <v>8.7089924271748111E-8</v>
+        <v>1.1657757212188209</v>
       </c>
       <c r="K46">
-        <v>8.7826804575359636E-8</v>
+        <v>1.175639516308528</v>
       </c>
       <c r="L46">
-        <v>8.856991972859805E-8</v>
+        <v>1.1855867703790679</v>
       </c>
       <c r="M46">
-        <v>8.9319322485417652E-8</v>
+        <v>1.1956181895888121</v>
       </c>
       <c r="N46">
-        <v>9.0075066046131511E-8</v>
+        <v>1.2057344860710391</v>
       </c>
       <c r="O46">
-        <v>9.0837204061188118E-8</v>
+        <v>1.2159363779844889</v>
       </c>
       <c r="P46">
-        <v>9.1605790634980167E-8</v>
+        <v>1.226224589564346</v>
       </c>
       <c r="Q46">
-        <v>9.2380880329685234E-8</v>
+        <v>1.2365998511736529</v>
       </c>
       <c r="R46">
-        <v>9.316252816913941E-8</v>
+        <v>1.247062899355156</v>
       </c>
       <c r="S46">
-        <v>9.3950789642743219E-8</v>
+        <v>1.2576144768835991</v>
       </c>
       <c r="T46">
-        <v>9.4745720709400996E-8</v>
+        <v>1.2682553328184429</v>
       </c>
       <c r="U46">
-        <v>9.5547377801493405E-8</v>
+        <v>1.278986222557055</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>0.55828914182499667</v>
+        <v>0.53255765199161353</v>
       </c>
       <c r="B47">
-        <v>8.0329418887455462E-8</v>
+        <v>1.083815641168882</v>
       </c>
       <c r="C47">
-        <v>8.1009097588220246E-8</v>
+        <v>1.092985960300535</v>
       </c>
       <c r="D47">
-        <v>8.1694527147670105E-8</v>
+        <v>1.102233870813768</v>
       </c>
       <c r="E47">
-        <v>8.2385756224642715E-8</v>
+        <v>1.1115600292203569</v>
       </c>
       <c r="F47">
-        <v>8.3082833889685232E-8</v>
+        <v>1.120965097586917</v>
       </c>
       <c r="G47">
-        <v>8.378580962853769E-8</v>
+        <v>1.130449743581905</v>
       </c>
       <c r="H47">
-        <v>8.4494733345646075E-8</v>
+        <v>1.1400146405230129</v>
       </c>
       <c r="I47">
-        <v>8.5209655367704969E-8</v>
+        <v>1.149660467424974</v>
       </c>
       <c r="J47">
-        <v>8.5930626447230362E-8</v>
+        <v>1.1593879090477599</v>
       </c>
       <c r="K47">
-        <v>8.6657697766162536E-8</v>
+        <v>1.1691976559451951</v>
       </c>
       <c r="L47">
-        <v>8.7390920939499503E-8</v>
+        <v>1.179090404513979</v>
       </c>
       <c r="M47">
-        <v>8.8130348018961098E-8</v>
+        <v>1.1890668570431211</v>
       </c>
       <c r="N47">
-        <v>8.887603149668424E-8</v>
+        <v>1.199127721763801</v>
       </c>
       <c r="O47">
-        <v>8.9628024308949306E-8</v>
+        <v>1.2092737128996429</v>
       </c>
       <c r="P47">
-        <v>9.0386379839938171E-8</v>
+        <v>1.21950555071742</v>
       </c>
       <c r="Q47">
-        <v>9.1151151925523797E-8</v>
+        <v>1.2298239615781821</v>
       </c>
       <c r="R47">
-        <v>9.1922394857092278E-8</v>
+        <v>1.240229677988828</v>
       </c>
       <c r="S47">
-        <v>9.270016338539684E-8</v>
+        <v>1.2507234386541</v>
       </c>
       <c r="T47">
-        <v>9.3484512724444631E-8</v>
+        <v>1.2613059885290281</v>
       </c>
       <c r="U47">
-        <v>9.4275498555416493E-8</v>
+        <v>1.271978078871812</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>0.56914141374979044</v>
+        <v>0.54857442348008323</v>
       </c>
       <c r="B48">
-        <v>7.9110221030270515E-8</v>
+        <v>1.0688870510701349</v>
       </c>
       <c r="C48">
-        <v>7.97795839236135E-8</v>
+        <v>1.077931057266091</v>
       </c>
       <c r="D48">
-        <v>8.0454610392119771E-8</v>
+        <v>1.087051586091814</v>
       </c>
       <c r="E48">
-        <v>8.1135348356108596E-8</v>
+        <v>1.096249285016218</v>
       </c>
       <c r="F48">
-        <v>8.1821846141360111E-8</v>
+        <v>1.1055248069865451</v>
       </c>
       <c r="G48">
-        <v>8.2514152482545659E-8</v>
+        <v>1.114878810474714</v>
       </c>
       <c r="H48">
-        <v>8.321231652668768E-8</v>
+        <v>1.124311959524072</v>
       </c>
       <c r="I48">
-        <v>8.3916387836648571E-8</v>
+        <v>1.133824923796529</v>
       </c>
       <c r="J48">
-        <v>8.4626416394649174E-8</v>
+        <v>1.1434183786201031</v>
       </c>
       <c r="K48">
-        <v>8.5342452605817111E-8</v>
+        <v>1.153093005036858</v>
       </c>
       <c r="L48">
-        <v>8.6064547301764945E-8</v>
+        <v>1.16284948985125</v>
       </c>
       <c r="M48">
-        <v>8.6792751744198778E-8</v>
+        <v>1.172688525678889</v>
       </c>
       <c r="N48">
-        <v>8.752711762855737E-8</v>
+        <v>1.182610810995703</v>
       </c>
       <c r="O48">
-        <v>8.8267697087681971E-8</v>
+        <v>1.1926170501875251</v>
       </c>
       <c r="P48">
-        <v>8.9014542695517255E-8</v>
+        <v>1.202707953600098</v>
       </c>
       <c r="Q48">
-        <v>8.9767707470843522E-8</v>
+        <v>1.2128842375894999</v>
       </c>
       <c r="R48">
-        <v>9.0527244881040618E-8</v>
+        <v>1.2231466245730021</v>
       </c>
       <c r="S48">
-        <v>9.1293208845883519E-8</v>
+        <v>1.2334958430803511</v>
       </c>
       <c r="T48">
-        <v>9.2065653741370097E-8</v>
+        <v>1.2439326278054861</v>
       </c>
       <c r="U48">
-        <v>9.2844634403581359E-8</v>
+        <v>1.2544577196586999</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>0.5811994947431931</v>
+        <v>0.56559224318658297</v>
       </c>
       <c r="B49">
-        <v>7.7349157458779739E-8</v>
+        <v>1.0435084479022709</v>
       </c>
       <c r="C49">
-        <v>7.8003619741402389E-8</v>
+        <v>1.052337722107541</v>
       </c>
       <c r="D49">
-        <v>7.8663619522990107E-8</v>
+        <v>1.0612417020644971</v>
       </c>
       <c r="E49">
-        <v>7.9329203657113487E-8</v>
+        <v>1.0702210198691879</v>
       </c>
       <c r="F49">
-        <v>8.0000419393777954E-8</v>
+        <v>1.0792763129659171</v>
       </c>
       <c r="G49">
-        <v>8.067731438277795E-8</v>
+        <v>1.0884082241924959</v>
       </c>
       <c r="H49">
-        <v>8.1359936677079679E-8</v>
+        <v>1.0976174018258771</v>
       </c>
       <c r="I49">
-        <v>8.2048334736232318E-8</v>
+        <v>1.1069044996281781</v>
       </c>
       <c r="J49">
-        <v>8.2742557429808217E-8</v>
+        <v>1.116270176893092</v>
       </c>
       <c r="K49">
-        <v>8.3442654040872202E-8</v>
+        <v>1.1257150984926889</v>
       </c>
       <c r="L49">
-        <v>8.4148674269480187E-8</v>
+        <v>1.1352399349246169</v>
       </c>
       <c r="M49">
-        <v>8.4860668236207268E-8</v>
+        <v>1.1448453623596999</v>
       </c>
       <c r="N49">
-        <v>8.5578686485705938E-8</v>
+        <v>1.154532062689942</v>
       </c>
       <c r="O49">
-        <v>8.6302779990294284E-8</v>
+        <v>1.16430072357693</v>
       </c>
       <c r="P49">
-        <v>8.7033000153574388E-8</v>
+        <v>1.174152038500657</v>
       </c>
       <c r="Q49">
-        <v>8.7769398814081577E-8</v>
+        <v>1.1840867068087459</v>
       </c>
       <c r="R49">
-        <v>8.8512028248964438E-8</v>
+        <v>1.1941054337661039</v>
       </c>
       <c r="S49">
-        <v>8.9260941177696056E-8</v>
+        <v>1.2042089306049819</v>
       </c>
       <c r="T49">
-        <v>9.0016190765816402E-8</v>
+        <v>1.2143979145754711</v>
       </c>
       <c r="U49">
-        <v>9.0777830628706777E-8</v>
+        <v>1.224673108996416</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>0.58843434361616875</v>
+        <v>0.57660377358490511</v>
       </c>
       <c r="B50">
-        <v>7.6129959601594236E-8</v>
+        <v>1.0226084217640281</v>
       </c>
       <c r="C50">
-        <v>7.6774106076795075E-8</v>
+        <v>1.031260857859321</v>
       </c>
       <c r="D50">
-        <v>7.742370276743919E-8</v>
+        <v>1.039986503453763</v>
       </c>
       <c r="E50">
-        <v>7.8078795788578785E-8</v>
+        <v>1.048785977983395</v>
       </c>
       <c r="F50">
-        <v>7.8739431645452238E-8</v>
+        <v>1.057659906125398</v>
       </c>
       <c r="G50">
-        <v>7.9405657236785337E-8</v>
+        <v>1.0666089178424309</v>
       </c>
       <c r="H50">
-        <v>8.0077519858120714E-8</v>
+        <v>1.075633648427361</v>
       </c>
       <c r="I50">
-        <v>8.0755067205175324E-8</v>
+        <v>1.0847347385483579</v>
       </c>
       <c r="J50">
-        <v>8.143834737722642E-8</v>
+        <v>1.0939128342943749</v>
       </c>
       <c r="K50">
-        <v>8.2127408880526168E-8</v>
+        <v>1.103168587221018</v>
       </c>
       <c r="L50">
-        <v>8.2822300631745007E-8</v>
+        <v>1.1125026543967991</v>
       </c>
       <c r="M50">
-        <v>8.352307196144434E-8</v>
+        <v>1.121915698449778</v>
       </c>
       <c r="N50">
-        <v>8.4229772617578459E-8</v>
+        <v>1.1314083876146059</v>
       </c>
       <c r="O50">
-        <v>8.4942452769026314E-8</v>
+        <v>1.140981395779967</v>
       </c>
       <c r="P50">
-        <v>8.566116300915285E-8</v>
+        <v>1.1506354025364089</v>
       </c>
       <c r="Q50">
-        <v>8.6385954359400654E-8</v>
+        <v>1.1603710932245941</v>
       </c>
       <c r="R50">
-        <v>8.7116878272912142E-8</v>
+        <v>1.1701891589839499</v>
       </c>
       <c r="S50">
-        <v>8.7853986638182101E-8</v>
+        <v>1.1800902968017351</v>
       </c>
       <c r="T50">
-        <v>8.8597331782741233E-8</v>
+        <v>1.190075209562514</v>
       </c>
       <c r="U50">
-        <v>8.9346966476871008E-8</v>
+        <v>1.200144606098061</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>0.60049242460957153</v>
+        <v>0.58661425576519866</v>
       </c>
       <c r="B51">
-        <v>7.3962496744376071E-8</v>
+        <v>1.0002155366159089</v>
       </c>
       <c r="C51">
-        <v>7.4588304006382642E-8</v>
+        <v>1.0086785033076551</v>
       </c>
       <c r="D51">
-        <v>7.5219406313127021E-8</v>
+        <v>1.017213076370832</v>
       </c>
       <c r="E51">
-        <v>7.5855848466739922E-8</v>
+        <v>1.0258198616771881</v>
       </c>
       <c r="F51">
-        <v>7.6497675648429344E-8</v>
+        <v>1.03449947022484</v>
       </c>
       <c r="G51">
-        <v>7.714493342168793E-8</v>
+        <v>1.0432525181816461</v>
       </c>
       <c r="H51">
-        <v>7.7797667735527561E-8</v>
+        <v>1.0520796269289501</v>
       </c>
       <c r="I51">
-        <v>7.8455924927741251E-8</v>
+        <v>1.0609814231056911</v>
       </c>
       <c r="J51">
-        <v>7.9119751728192736E-8</v>
+        <v>1.06995853865289</v>
       </c>
       <c r="K51">
-        <v>7.9789195262133781E-8</v>
+        <v>1.0790116108585119</v>
       </c>
       <c r="L51">
-        <v>8.046430305354974E-8</v>
+        <v>1.0881412824027059</v>
       </c>
       <c r="M51">
-        <v>8.1145123028533058E-8</v>
+        <v>1.0973482014034299</v>
       </c>
       <c r="N51">
-        <v>8.1831703518685769E-8</v>
+        <v>1.10663302146246</v>
       </c>
       <c r="O51">
-        <v>8.2524093264550556E-8</v>
+        <v>1.11599640171179</v>
       </c>
       <c r="P51">
-        <v>8.3222341419070711E-8</v>
+        <v>1.125439006860427</v>
       </c>
       <c r="Q51">
-        <v>8.3926497551079658E-8</v>
+        <v>1.1349615072415711</v>
       </c>
       <c r="R51">
-        <v>8.463661164881981E-8</v>
+        <v>1.144564578860211</v>
       </c>
       <c r="S51">
-        <v>8.5352734123491261E-8</v>
+        <v>1.154248903441111</v>
       </c>
       <c r="T51">
-        <v>8.6074915812830423E-8</v>
+        <v>1.1640151684772011</v>
       </c>
       <c r="U51">
-        <v>8.6803207984719155E-8</v>
+        <v>1.1738640672783931</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>0.61134469653436518</v>
+        <v>0.599627882599581</v>
       </c>
       <c r="B52">
-        <v>7.1930500315733526E-8</v>
+        <v>0.96587977938879521</v>
       </c>
       <c r="C52">
-        <v>7.2539114565370446E-8</v>
+        <v>0.97405222632843647</v>
       </c>
       <c r="D52">
-        <v>7.3152878387208817E-8</v>
+        <v>0.98229382151034017</v>
       </c>
       <c r="E52">
-        <v>7.3771835352515423E-8</v>
+        <v>0.99060515000767213</v>
       </c>
       <c r="F52">
-        <v>7.4396029401219813E-8</v>
+        <v>0.99898680184398669</v>
       </c>
       <c r="G52">
-        <v>7.502550484503354E-8</v>
+        <v>1.007439372035112</v>
       </c>
       <c r="H52">
-        <v>7.5660306370595909E-8</v>
+        <v>1.015963460631389</v>
       </c>
       <c r="I52">
-        <v>7.6300479042646235E-8</v>
+        <v>1.024559672760271</v>
       </c>
       <c r="J52">
-        <v>7.6946068307223073E-8</v>
+        <v>1.0332286186692829</v>
       </c>
       <c r="K52">
-        <v>7.7597119994890368E-8</v>
+        <v>1.0419709137693389</v>
       </c>
       <c r="L52">
-        <v>7.8253680323991093E-8</v>
+        <v>1.050787178678434</v>
       </c>
       <c r="M52">
-        <v>7.8915795903928151E-8</v>
+        <v>1.0596780392656999</v>
       </c>
       <c r="N52">
-        <v>7.9583513738473287E-8</v>
+        <v>1.068644126695838</v>
       </c>
       <c r="O52">
-        <v>8.0256881229103917E-8</v>
+        <v>1.077686077473923</v>
       </c>
       <c r="P52">
-        <v>8.0935946178368112E-8</v>
+        <v>1.0868045334905909</v>
       </c>
       <c r="Q52">
-        <v>8.1620756793278107E-8</v>
+        <v>1.0960001420676071</v>
       </c>
       <c r="R52">
-        <v>8.2311361688732641E-8</v>
+        <v>1.105273556003816</v>
       </c>
       <c r="S52">
-        <v>8.3007809890967984E-8</v>
+        <v>1.11462543362149</v>
       </c>
       <c r="T52">
-        <v>8.3710150841038443E-8</v>
+        <v>1.1240564388130581</v>
       </c>
       <c r="U52">
-        <v>8.4418434398326158E-8</v>
+        <v>1.1335672410882389</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>0.62099116215988914</v>
+        <v>0.6116404612159333</v>
       </c>
       <c r="B53">
-        <v>6.9898503887090439E-8</v>
+        <v>0.93303688117155803</v>
       </c>
       <c r="C53">
-        <v>7.0489925124357708E-8</v>
+        <v>0.94093143965266435</v>
       </c>
       <c r="D53">
-        <v>7.1086350461290071E-8</v>
+        <v>0.94889279512204583</v>
       </c>
       <c r="E53">
-        <v>7.1687822238290369E-8</v>
+        <v>0.95692151275857218</v>
       </c>
       <c r="F53">
-        <v>7.2294383154009726E-8</v>
+        <v>0.96501816252317285</v>
       </c>
       <c r="G53">
-        <v>7.2906076268378606E-8</v>
+        <v>0.97318331919929801</v>
       </c>
       <c r="H53">
-        <v>7.3522945005663701E-8</v>
+        <v>0.98141756243372347</v>
       </c>
       <c r="I53">
-        <v>7.4145033157550663E-8</v>
+        <v>0.98972147677769828</v>
       </c>
       <c r="J53">
-        <v>7.4772384886252829E-8</v>
+        <v>0.99809565172844361</v>
       </c>
       <c r="K53">
-        <v>7.540504472764636E-8</v>
+        <v>1.006540681771001</v>
       </c>
       <c r="L53">
-        <v>7.6043057594431863E-8</v>
+        <v>1.015057166420436</v>
       </c>
       <c r="M53">
-        <v>7.6686468779322662E-8</v>
+        <v>1.023645710264395</v>
       </c>
       <c r="N53">
-        <v>7.7335323958260196E-8</v>
+        <v>1.0323069230060271</v>
       </c>
       <c r="O53">
-        <v>7.7989669193656682E-8</v>
+        <v>1.041041419507269</v>
       </c>
       <c r="P53">
-        <v>7.8649550937664918E-8</v>
+        <v>1.049849819832489</v>
       </c>
       <c r="Q53">
-        <v>7.9315016035475948E-8</v>
+        <v>1.058732749292512</v>
       </c>
       <c r="R53">
-        <v>7.9986111728644851E-8</v>
+        <v>1.0676908384890049</v>
       </c>
       <c r="S53">
-        <v>8.0662885658444085E-8</v>
+        <v>1.076724723359247</v>
       </c>
       <c r="T53">
-        <v>8.1345385869245816E-8</v>
+        <v>1.0858350452212711</v>
       </c>
       <c r="U53">
-        <v>8.2033660811932513E-8</v>
+        <v>1.095022450819398</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>0.6306376264007435</v>
+        <v>0.62265199161425555</v>
       </c>
       <c r="B54">
-        <v>6.7460108172719393E-8</v>
+        <v>0.90168684196419691</v>
       </c>
       <c r="C54">
-        <v>6.8030897795143093E-8</v>
+        <v>0.90931614328033816</v>
       </c>
       <c r="D54">
-        <v>6.8606516950188251E-8</v>
+        <v>0.91700999720594834</v>
       </c>
       <c r="E54">
-        <v>6.9187006501221004E-8</v>
+        <v>0.92476894992988734</v>
       </c>
       <c r="F54">
-        <v>6.977240765735832E-8</v>
+        <v>0.93259355226239748</v>
       </c>
       <c r="G54">
-        <v>7.0362761976393367E-8</v>
+        <v>0.94048435967420507</v>
       </c>
       <c r="H54">
-        <v>7.0958111367745745E-8</v>
+        <v>0.94844193233595364</v>
       </c>
       <c r="I54">
-        <v>7.1558498095436676E-8</v>
+        <v>0.95646683515797093</v>
       </c>
       <c r="J54">
-        <v>7.2163964781089247E-8</v>
+        <v>0.96455963783037135</v>
       </c>
       <c r="K54">
-        <v>7.2774554406954265E-8</v>
+        <v>0.97272091486349921</v>
       </c>
       <c r="L54">
-        <v>7.3390310318961516E-8</v>
+        <v>0.98095124562871305</v>
       </c>
       <c r="M54">
-        <v>7.4011276229796778E-8</v>
+        <v>0.9892512143995148</v>
       </c>
       <c r="N54">
-        <v>7.4637496222005239E-8</v>
+        <v>0.99762141039302832</v>
       </c>
       <c r="O54">
-        <v>7.5269014751120741E-8</v>
+        <v>1.006062427811828</v>
       </c>
       <c r="P54">
-        <v>7.5905876648821816E-8</v>
+        <v>1.0145748658861209</v>
       </c>
       <c r="Q54">
-        <v>7.6548127126114129E-8</v>
+        <v>1.023159328916287</v>
       </c>
       <c r="R54">
-        <v>7.7195811776540246E-8</v>
+        <v>1.0318164263157781</v>
       </c>
       <c r="S54">
-        <v>7.7848976579416173E-8</v>
+        <v>1.04054677265438</v>
       </c>
       <c r="T54">
-        <v>7.8507667903095438E-8</v>
+        <v>1.0493509877018401</v>
       </c>
       <c r="U54">
-        <v>7.9171932508260949E-8</v>
+        <v>1.05822969647187</v>
       </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>0.64028409064159797</v>
+        <v>0.63166142557652039</v>
       </c>
       <c r="B55">
-        <v>6.5428111744076835E-8</v>
+        <v>0.87033680275682823</v>
       </c>
       <c r="C55">
-        <v>6.5981708354130884E-8</v>
+        <v>0.87770084690800432</v>
       </c>
       <c r="D55">
-        <v>6.6539989024270047E-8</v>
+        <v>0.88512719928984329</v>
       </c>
       <c r="E55">
-        <v>6.7102993386996506E-8</v>
+        <v>0.89261638710119495</v>
       </c>
       <c r="F55">
-        <v>6.7670761410148789E-8</v>
+        <v>0.90016894200161446</v>
       </c>
       <c r="G55">
-        <v>6.8243333399738976E-8</v>
+        <v>0.90778540014910403</v>
       </c>
       <c r="H55">
-        <v>6.8820750002814106E-8</v>
+        <v>0.91546630223817604</v>
       </c>
       <c r="I55">
-        <v>6.940305221034166E-8</v>
+        <v>0.9232121935382358</v>
       </c>
       <c r="J55">
-        <v>6.9990281360119585E-8</v>
+        <v>0.93102362393229099</v>
       </c>
       <c r="K55">
-        <v>7.0582479139710839E-8</v>
+        <v>0.93890114795598889</v>
       </c>
       <c r="L55">
-        <v>7.1179687589402856E-8</v>
+        <v>0.94684532483698181</v>
       </c>
       <c r="M55">
-        <v>7.1781949105191871E-8</v>
+        <v>0.9548567185346265</v>
       </c>
       <c r="N55">
-        <v>7.2389306441792744E-8</v>
+        <v>0.9629358977800212</v>
       </c>
       <c r="O55">
-        <v>7.3001802715674116E-8</v>
+        <v>0.97108343611637904</v>
       </c>
       <c r="P55">
-        <v>7.3619481408119218E-8</v>
+        <v>0.97929991193974486</v>
       </c>
       <c r="Q55">
-        <v>7.4242386368312592E-8</v>
+        <v>0.98758590854005401</v>
       </c>
       <c r="R55">
-        <v>7.4870561816453064E-8</v>
+        <v>0.99594201414254258</v>
       </c>
       <c r="S55">
-        <v>7.5504052346892896E-8</v>
+        <v>1.0043688219495039</v>
       </c>
       <c r="T55">
-        <v>7.6142902931303445E-8</v>
+        <v>1.0128669301824</v>
       </c>
       <c r="U55">
-        <v>7.6787158921867953E-8</v>
+        <v>1.021436942124333</v>
       </c>
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>0.64872474719851292</v>
+        <v>0.63966981132075518</v>
       </c>
       <c r="B56">
-        <v>6.326064888685814E-8</v>
+        <v>0.8479439176087088</v>
       </c>
       <c r="C56">
-        <v>6.3795906283717895E-8</v>
+        <v>0.8551184923563383</v>
       </c>
       <c r="D56">
-        <v>6.4335692569957322E-8</v>
+        <v>0.86235377220691223</v>
       </c>
       <c r="E56">
-        <v>6.4880046065157074E-8</v>
+        <v>0.86965027079498725</v>
       </c>
       <c r="F56">
-        <v>6.5429005413125326E-8</v>
+        <v>0.8770085061010563</v>
       </c>
       <c r="G56">
-        <v>6.5982609584641E-8</v>
+        <v>0.88442900048831885</v>
       </c>
       <c r="H56">
-        <v>6.654089788022037E-8</v>
+        <v>0.89191228073976458</v>
       </c>
       <c r="I56">
-        <v>6.7103909932907004E-8</v>
+        <v>0.8994588780955689</v>
       </c>
       <c r="J56">
-        <v>6.7671685711085292E-8</v>
+        <v>0.90706932829080633</v>
       </c>
       <c r="K56">
-        <v>6.8244265521317883E-8</v>
+        <v>0.91474417159348276</v>
       </c>
       <c r="L56">
-        <v>6.8821690011207006E-8</v>
+        <v>0.9224839528428892</v>
       </c>
       <c r="M56">
-        <v>6.9404000172280007E-8</v>
+        <v>0.93028922148827886</v>
       </c>
       <c r="N56">
-        <v>6.9991237342899445E-8</v>
+        <v>0.93816053162787427</v>
       </c>
       <c r="O56">
-        <v>7.0583443211197736E-8</v>
+        <v>0.94609844204820248</v>
       </c>
       <c r="P56">
-        <v>7.1180659818036469E-8</v>
+        <v>0.954103516263763</v>
       </c>
       <c r="Q56">
-        <v>7.1782929559990973E-8</v>
+        <v>0.96217632255703156</v>
       </c>
       <c r="R56">
-        <v>7.2390295192360097E-8</v>
+        <v>0.97031743401880421</v>
       </c>
       <c r="S56">
-        <v>7.3002799832201421E-8</v>
+        <v>0.97852742858887976</v>
       </c>
       <c r="T56">
-        <v>7.3620486961392013E-8</v>
+        <v>0.9868068890970878</v>
       </c>
       <c r="U56">
-        <v>7.4243400429715451E-8</v>
+        <v>0.99515640330466526</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>0.65716540375542776</v>
+        <v>0.64968029350104883</v>
       </c>
       <c r="B57">
-        <v>6.1093186029639989E-8</v>
+        <v>0.81510101939147162</v>
       </c>
       <c r="C57">
-        <v>6.1610104213305475E-8</v>
+        <v>0.82199770568056618</v>
       </c>
       <c r="D57">
-        <v>6.2131396115645166E-8</v>
+        <v>0.82895274581861789</v>
       </c>
       <c r="E57">
-        <v>6.2657098743318211E-8</v>
+        <v>0.83596663354588718</v>
       </c>
       <c r="F57">
-        <v>6.3187249416102433E-8</v>
+        <v>0.84303986678024212</v>
       </c>
       <c r="G57">
-        <v>6.3721885769543593E-8</v>
+        <v>0.85017294765250528</v>
       </c>
       <c r="H57">
-        <v>6.426104575762723E-8</v>
+        <v>0.85736638254209918</v>
       </c>
       <c r="I57">
-        <v>6.4804767655472958E-8</v>
+        <v>0.8646206821129957</v>
       </c>
       <c r="J57">
-        <v>6.5353090062051607E-8</v>
+        <v>0.87193636134996677</v>
       </c>
       <c r="K57">
-        <v>6.5906051902925536E-8</v>
+        <v>0.87931393959514526</v>
       </c>
       <c r="L57">
-        <v>6.6463692433011739E-8</v>
+        <v>0.88675394058489143</v>
       </c>
       <c r="M57">
-        <v>6.7026051239368739E-8</v>
+        <v>0.89425689248697382</v>
       </c>
       <c r="N57">
-        <v>6.7593168244006782E-8</v>
+        <v>0.90182332793806386</v>
       </c>
       <c r="O57">
-        <v>6.8165083706721978E-8</v>
+        <v>0.90945378408154842</v>
       </c>
       <c r="P57">
-        <v>6.8741838227954356E-8</v>
+        <v>0.91714880260566101</v>
       </c>
       <c r="Q57">
-        <v>6.9323472751669991E-8</v>
+        <v>0.92490892978193684</v>
       </c>
       <c r="R57">
-        <v>6.9910028568267778E-8</v>
+        <v>0.93273471650399298</v>
       </c>
       <c r="S57">
-        <v>7.0501547317510594E-8</v>
+        <v>0.94062671832663591</v>
       </c>
       <c r="T57">
-        <v>7.1098070991481243E-8</v>
+        <v>0.9485854955053008</v>
       </c>
       <c r="U57">
-        <v>7.1699641937563612E-8</v>
+        <v>0.95661161303582432</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>0.66560606031234282</v>
+        <v>0.65768867924528229</v>
       </c>
       <c r="B58">
-        <v>5.9061189600996881E-8</v>
+        <v>0.79121527523348367</v>
       </c>
       <c r="C58">
-        <v>5.9560914772292711E-8</v>
+        <v>0.79790986082546178</v>
       </c>
       <c r="D58">
-        <v>6.0064868189726393E-8</v>
+        <v>0.80466109026349741</v>
       </c>
       <c r="E58">
-        <v>6.0573085629093143E-8</v>
+        <v>0.81146944281927158</v>
       </c>
       <c r="F58">
-        <v>6.1085603168892319E-8</v>
+        <v>0.81833540181965303</v>
       </c>
       <c r="G58">
-        <v>6.1602457192888621E-8</v>
+        <v>0.82525945468100725</v>
       </c>
       <c r="H58">
-        <v>6.2123684392694996E-8</v>
+        <v>0.83224209294380003</v>
       </c>
       <c r="I58">
-        <v>6.2649321770377346E-8</v>
+        <v>0.83928381230749072</v>
       </c>
       <c r="J58">
-        <v>6.3179406641081336E-8</v>
+        <v>0.84638511266572281</v>
       </c>
       <c r="K58">
-        <v>6.3713976635681488E-8</v>
+        <v>0.85354649814181172</v>
       </c>
       <c r="L58">
-        <v>6.4253069703452484E-8</v>
+        <v>0.86076847712453253</v>
       </c>
       <c r="M58">
-        <v>6.4796724114763209E-8</v>
+        <v>0.86805156230420966</v>
       </c>
       <c r="N58">
-        <v>6.5344978463793665E-8</v>
+        <v>0.87539627070911374</v>
       </c>
       <c r="O58">
-        <v>6.5897871671274717E-8</v>
+        <v>0.88280312374216663</v>
       </c>
       <c r="P58">
-        <v>6.6455442987251123E-8</v>
+        <v>0.89027264721795374</v>
       </c>
       <c r="Q58">
-        <v>6.7017731993867805E-8</v>
+        <v>0.8978053714000529</v>
       </c>
       <c r="R58">
-        <v>6.7584778608179961E-8</v>
+        <v>0.90540183103867888</v>
       </c>
       <c r="S58">
-        <v>6.8156623084986669E-8</v>
+        <v>0.91306256540864383</v>
       </c>
       <c r="T58">
-        <v>6.8733306019688588E-8</v>
+        <v>0.92078811834764085</v>
       </c>
       <c r="U58">
-        <v>6.9314868351169954E-8</v>
+        <v>0.92857903829485222</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>0.67525252593786678</v>
+        <v>0.66669811320754713</v>
       </c>
       <c r="B59">
-        <v>5.743559245808285E-8</v>
+        <v>0.7643438130557435</v>
       </c>
       <c r="C59">
-        <v>5.7921563219482969E-8</v>
+        <v>0.77081103536346585</v>
       </c>
       <c r="D59">
-        <v>5.8411645848991853E-8</v>
+        <v>0.77733297776398314</v>
       </c>
       <c r="E59">
-        <v>5.8905875137713563E-8</v>
+        <v>0.78391010325182553</v>
       </c>
       <c r="F59">
-        <v>5.9404286171124722E-8</v>
+        <v>0.79054287873898632</v>
       </c>
       <c r="G59">
-        <v>5.9906914331565132E-8</v>
+        <v>0.79723177508806831</v>
       </c>
       <c r="H59">
-        <v>6.04137953007497E-8</v>
+        <v>0.8039772671457095</v>
       </c>
       <c r="I59">
-        <v>6.0924965062301354E-8</v>
+        <v>0.8107798337762937</v>
       </c>
       <c r="J59">
-        <v>6.1440459904305633E-8</v>
+        <v>0.81763995789594435</v>
       </c>
       <c r="K59">
-        <v>6.1960316421886771E-8</v>
+        <v>0.82455812650680771</v>
       </c>
       <c r="L59">
-        <v>6.248457151980559E-8</v>
+        <v>0.83153483073162482</v>
       </c>
       <c r="M59">
-        <v>6.3013262415079305E-8</v>
+        <v>0.83857056584859579</v>
       </c>
       <c r="N59">
-        <v>6.3546426639623697E-8</v>
+        <v>0.84566583132654105</v>
       </c>
       <c r="O59">
-        <v>6.4084102042917445E-8</v>
+        <v>0.85282113086035805</v>
       </c>
       <c r="P59">
-        <v>6.4626326794689068E-8</v>
+        <v>0.86003697240677879</v>
       </c>
       <c r="Q59">
-        <v>6.5173139387626588E-8</v>
+        <v>0.86731386822042933</v>
       </c>
       <c r="R59">
-        <v>6.5724578640110242E-8</v>
+        <v>0.87465233489019634</v>
       </c>
       <c r="S59">
-        <v>6.6280683698968066E-8</v>
+        <v>0.88205289337589832</v>
       </c>
       <c r="T59">
-        <v>6.6841494042255021E-8</v>
+        <v>0.88951606904526903</v>
       </c>
       <c r="U59">
-        <v>6.7407049482055577E-8</v>
+        <v>0.89704239171125433</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>0.68369318249478161</v>
+        <v>0.67570754716981063</v>
       </c>
       <c r="B60">
-        <v>5.4726263886560029E-8</v>
+        <v>0.73747235087800234</v>
       </c>
       <c r="C60">
-        <v>5.5189310631467282E-8</v>
+        <v>0.74371220990146891</v>
       </c>
       <c r="D60">
-        <v>5.5656275281101513E-8</v>
+        <v>0.75000486526446808</v>
       </c>
       <c r="E60">
-        <v>5.6127190985414829E-8</v>
+        <v>0.75635076368437837</v>
       </c>
       <c r="F60">
-        <v>5.6602091174845949E-8</v>
+        <v>0.76275035565831883</v>
       </c>
       <c r="G60">
-        <v>5.7081009562693218E-8</v>
+        <v>0.76920409549512825</v>
       </c>
       <c r="H60">
-        <v>5.7563980147508113E-8</v>
+        <v>0.77571244134761808</v>
       </c>
       <c r="I60">
-        <v>5.8051037215508617E-8</v>
+        <v>0.7822758552450958</v>
       </c>
       <c r="J60">
-        <v>5.8542215343013372E-8</v>
+        <v>0.788894803126165</v>
       </c>
       <c r="K60">
-        <v>5.9037549398896158E-8</v>
+        <v>0.7955697548718027</v>
       </c>
       <c r="L60">
-        <v>5.9537074547061347E-8</v>
+        <v>0.802301184338716</v>
       </c>
       <c r="M60">
-        <v>6.0040826248940064E-8</v>
+        <v>0.80908956939298105</v>
       </c>
       <c r="N60">
-        <v>6.054884026600769E-8</v>
+        <v>0.81593539194396725</v>
       </c>
       <c r="O60">
-        <v>6.1061152662322579E-8</v>
+        <v>0.82283913797854846</v>
       </c>
       <c r="P60">
-        <v>6.1577799807086247E-8</v>
+        <v>0.82980129759560295</v>
       </c>
       <c r="Q60">
-        <v>6.2098818377225191E-8</v>
+        <v>0.83682236504080487</v>
       </c>
       <c r="R60">
-        <v>6.2624245359994661E-8</v>
+        <v>0.8439028387417129</v>
       </c>
       <c r="S60">
-        <v>6.3154118055604367E-8</v>
+        <v>0.8510432213431518</v>
       </c>
       <c r="T60">
-        <v>6.3688474079866372E-8</v>
+        <v>0.8582440197428961</v>
       </c>
       <c r="U60">
-        <v>6.4227351366865586E-8</v>
+        <v>0.86550574512765555</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>0.69333964673563608</v>
+        <v>0.68171383647798689</v>
       </c>
       <c r="B61">
-        <v>5.2829733886493613E-8</v>
+        <v>0.71507946572988534</v>
       </c>
       <c r="C61">
-        <v>5.3276733819855867E-8</v>
+        <v>0.72112985534980523</v>
       </c>
       <c r="D61">
-        <v>5.3727515883577817E-8</v>
+        <v>0.72723143818153924</v>
       </c>
       <c r="E61">
-        <v>5.4182112078805263E-8</v>
+        <v>0.73338464737817299</v>
       </c>
       <c r="F61">
-        <v>5.464055467745035E-8</v>
+        <v>0.739589919757763</v>
       </c>
       <c r="G61">
-        <v>5.5102876224482439E-8</v>
+        <v>0.74584769583434551</v>
       </c>
       <c r="H61">
-        <v>5.5569109540238538E-8</v>
+        <v>0.75215841984920895</v>
       </c>
       <c r="I61">
-        <v>5.6039287722753241E-8</v>
+        <v>0.75852253980243134</v>
       </c>
       <c r="J61">
-        <v>5.6513444150108307E-8</v>
+        <v>0.76494050748468267</v>
       </c>
       <c r="K61">
-        <v>5.6991612482802262E-8</v>
+        <v>0.77141277850929901</v>
       </c>
       <c r="L61">
-        <v>5.7473826666139909E-8</v>
+        <v>0.77793981234462595</v>
       </c>
       <c r="M61">
-        <v>5.7960120932642107E-8</v>
+        <v>0.78452207234663585</v>
       </c>
       <c r="N61">
-        <v>5.8450529804475978E-8</v>
+        <v>0.79116002579182299</v>
       </c>
       <c r="O61">
-        <v>5.8945088095905687E-8</v>
+        <v>0.79785414391037435</v>
       </c>
       <c r="P61">
-        <v>5.944383091576378E-8</v>
+        <v>0.80460490191962353</v>
       </c>
       <c r="Q61">
-        <v>5.9946793669943707E-8</v>
+        <v>0.81141277905778497</v>
       </c>
       <c r="R61">
-        <v>6.0454012063913252E-8</v>
+        <v>0.81827825861797709</v>
       </c>
       <c r="S61">
-        <v>6.0965522105249248E-8</v>
+        <v>0.82520182798253028</v>
       </c>
       <c r="T61">
-        <v>6.1481360106193793E-8</v>
+        <v>0.83218397865758609</v>
       </c>
       <c r="U61">
-        <v>6.2001562686232081E-8</v>
+        <v>0.83922520630799047</v>
       </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>0.70178030329255103</v>
+        <v>0.69572851153039772</v>
       </c>
       <c r="B62">
-        <v>5.1068670315003413E-8</v>
+        <v>0.67029369543365025</v>
       </c>
       <c r="C62">
-        <v>5.1500769637645299E-8</v>
+        <v>0.67596514624647708</v>
       </c>
       <c r="D62">
-        <v>5.1936525014448722E-8</v>
+        <v>0.68168458401568088</v>
       </c>
       <c r="E62">
-        <v>5.237596737981071E-8</v>
+        <v>0.68745241476576124</v>
       </c>
       <c r="F62">
-        <v>5.2819127929868768E-8</v>
+        <v>0.69326904795665045</v>
       </c>
       <c r="G62">
-        <v>5.3266038124715312E-8</v>
+        <v>0.69913489651277883</v>
       </c>
       <c r="H62">
-        <v>5.3716729690631133E-8</v>
+        <v>0.70505037685239003</v>
       </c>
       <c r="I62">
-        <v>5.417123462233757E-8</v>
+        <v>0.71101590891710165</v>
       </c>
       <c r="J62">
-        <v>5.462958518526794E-8</v>
+        <v>0.71703191620171713</v>
       </c>
       <c r="K62">
-        <v>5.5091813917857962E-8</v>
+        <v>0.72309882578429052</v>
       </c>
       <c r="L62">
-        <v>5.555795363385576E-8</v>
+        <v>0.72921706835644473</v>
       </c>
       <c r="M62">
-        <v>5.6028037424651192E-8</v>
+        <v>0.73538707825394467</v>
       </c>
       <c r="N62">
-        <v>5.6502098661625168E-8</v>
+        <v>0.74160929348753324</v>
       </c>
       <c r="O62">
-        <v>5.6980170998518608E-8</v>
+        <v>0.74788415577402523</v>
       </c>
       <c r="P62">
-        <v>5.7462288373821528E-8</v>
+        <v>0.7542121105676638</v>
       </c>
       <c r="Q62">
-        <v>5.7948485013182383E-8</v>
+        <v>0.76059360709174417</v>
       </c>
       <c r="R62">
-        <v>5.8438795431837708E-8</v>
+        <v>0.76702909837050459</v>
       </c>
       <c r="S62">
-        <v>5.8933254437062427E-8</v>
+        <v>0.77351904126128612</v>
       </c>
       <c r="T62">
-        <v>5.9431897130640753E-8</v>
+        <v>0.78006389648696473</v>
       </c>
       <c r="U62">
-        <v>5.9934758911358161E-8</v>
+        <v>0.78666412866865898</v>
       </c>
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>0.71624999965383263</v>
+        <v>0.71274633123689735</v>
       </c>
       <c r="B63">
-        <v>4.7952942457751508E-8</v>
+        <v>0.62252220711766604</v>
       </c>
       <c r="C63">
-        <v>4.8358679161426623E-8</v>
+        <v>0.62778945653626028</v>
       </c>
       <c r="D63">
-        <v>4.8767848861374163E-8</v>
+        <v>0.63310127290543161</v>
       </c>
       <c r="E63">
-        <v>4.9180480604666502E-8</v>
+        <v>0.63845803331252193</v>
       </c>
       <c r="F63">
-        <v>4.9596603684147512E-8</v>
+        <v>0.6438601180354635</v>
       </c>
       <c r="G63">
-        <v>5.001624764051194E-8</v>
+        <v>0.64930791056977422</v>
       </c>
       <c r="H63">
-        <v>5.0439442264402619E-8</v>
+        <v>0.65480179765578295</v>
       </c>
       <c r="I63">
-        <v>5.0866217598525253E-8</v>
+        <v>0.66034216930608292</v>
       </c>
       <c r="J63">
-        <v>5.1296603939781138E-8</v>
+        <v>0.66592941883322032</v>
       </c>
       <c r="K63">
-        <v>5.1730631841418072E-8</v>
+        <v>0.67156394287761489</v>
       </c>
       <c r="L63">
-        <v>5.2168332115199188E-8</v>
+        <v>0.67724614143571782</v>
       </c>
       <c r="M63">
-        <v>5.260973583359036E-8</v>
+        <v>0.68297641788840702</v>
       </c>
       <c r="N63">
-        <v>5.305487433196605E-8</v>
+        <v>0.68875517902962424</v>
       </c>
       <c r="O63">
-        <v>5.3503779210833799E-8</v>
+        <v>0.69458283509525254</v>
       </c>
       <c r="P63">
-        <v>5.3956482338077582E-8</v>
+        <v>0.70045979979223982</v>
       </c>
       <c r="Q63">
-        <v>5.441301585122003E-8</v>
+        <v>0.70638649032796696</v>
       </c>
       <c r="R63">
-        <v>5.4873412159704049E-8</v>
+        <v>0.71236332743986697</v>
       </c>
       <c r="S63">
-        <v>5.5337703947193412E-8</v>
+        <v>0.71839073542529219</v>
       </c>
       <c r="T63">
-        <v>5.5805924173893051E-8</v>
+        <v>0.72446914217163505</v>
       </c>
       <c r="U63">
-        <v>5.627810607888892E-8</v>
+        <v>0.73059897918670524</v>
       </c>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>0.73071969739978371</v>
+        <v>0.72676100628930851</v>
       </c>
       <c r="B64">
-        <v>4.5243613886228183E-8</v>
+        <v>0.58520073187080346</v>
       </c>
       <c r="C64">
-        <v>4.5626426573410433E-8</v>
+        <v>0.59015219895015336</v>
       </c>
       <c r="D64">
-        <v>4.60124782934833E-8</v>
+        <v>0.5951455611005495</v>
       </c>
       <c r="E64">
-        <v>4.6401796452367258E-8</v>
+        <v>0.60018117280217875</v>
       </c>
       <c r="F64">
-        <v>4.6794408687868223E-8</v>
+        <v>0.60525939153453623</v>
       </c>
       <c r="G64">
-        <v>4.719034287163951E-8</v>
+        <v>0.6103805778018021</v>
       </c>
       <c r="H64">
-        <v>4.7589627111160509E-8</v>
+        <v>0.6155450951584337</v>
       </c>
       <c r="I64">
-        <v>4.799228975173198E-8</v>
+        <v>0.62075331023497471</v>
       </c>
       <c r="J64">
-        <v>4.8398359378488341E-8</v>
+        <v>0.62600559276408219</v>
       </c>
       <c r="K64">
-        <v>4.8807864818426923E-8</v>
+        <v>0.63130231560677441</v>
       </c>
       <c r="L64">
-        <v>4.9220835142454423E-8</v>
+        <v>0.63664385477890006</v>
       </c>
       <c r="M64">
-        <v>4.963729966745057E-8</v>
+        <v>0.64203058947783087</v>
       </c>
       <c r="N64">
-        <v>5.005728795834948E-8</v>
+        <v>0.64746290210938284</v>
       </c>
       <c r="O64">
-        <v>5.0480829830238377E-8</v>
+        <v>0.65294117831496157</v>
       </c>
       <c r="P64">
-        <v>5.0907955350474213E-8</v>
+        <v>0.65846580699893986</v>
       </c>
       <c r="Q64">
-        <v>5.1338694840818057E-8</v>
+        <v>0.66403718035626613</v>
       </c>
       <c r="R64">
-        <v>5.1773078879587912E-8</v>
+        <v>0.66965569390030655</v>
       </c>
       <c r="S64">
-        <v>5.2211138303829131E-8</v>
+        <v>0.67532174649092203</v>
       </c>
       <c r="T64">
-        <v>5.2652904211503807E-8</v>
+        <v>0.68103574036278391</v>
       </c>
       <c r="U64">
-        <v>5.3098407963698353E-8</v>
+        <v>0.68679808115392904</v>
       </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>0.74398358607712578</v>
+        <v>0.7397746331236893</v>
       </c>
       <c r="B65">
-        <v>4.2805218171857137E-8</v>
+        <v>0.55982212870293702</v>
       </c>
       <c r="C65">
-        <v>4.3167399244195797E-8</v>
+        <v>0.56455886379160092</v>
       </c>
       <c r="D65">
-        <v>4.3532644782381473E-8</v>
+        <v>0.56933567707322974</v>
       </c>
       <c r="E65">
-        <v>4.3900980715297881E-8</v>
+        <v>0.57415290765514559</v>
       </c>
       <c r="F65">
-        <v>4.4272433191216798E-8</v>
+        <v>0.579010897513906</v>
       </c>
       <c r="G65">
-        <v>4.464702857965427E-8</v>
+        <v>0.58390999151958123</v>
       </c>
       <c r="H65">
-        <v>4.5024793473242547E-8</v>
+        <v>0.58885053746023641</v>
       </c>
       <c r="I65">
-        <v>4.5405754689617979E-8</v>
+        <v>0.59383288606662132</v>
       </c>
       <c r="J65">
-        <v>4.5789939273324753E-8</v>
+        <v>0.59885739103706859</v>
       </c>
       <c r="K65">
-        <v>4.6177374497734821E-8</v>
+        <v>0.60392440906260314</v>
       </c>
       <c r="L65">
-        <v>4.6568087866984062E-8</v>
+        <v>0.6090342998522642</v>
       </c>
       <c r="M65">
-        <v>4.6962107117924693E-8</v>
+        <v>0.61418742615863942</v>
       </c>
       <c r="N65">
-        <v>4.7359460222094509E-8</v>
+        <v>0.61938415380361878</v>
       </c>
       <c r="O65">
-        <v>4.7760175387702437E-8</v>
+        <v>0.62462485170436377</v>
       </c>
       <c r="P65">
-        <v>4.8164281061631097E-8</v>
+        <v>0.6299098918994962</v>
       </c>
       <c r="Q65">
-        <v>4.8571805931456232E-8</v>
+        <v>0.63523964957550982</v>
       </c>
       <c r="R65">
-        <v>4.8982778927483301E-8</v>
+        <v>0.6406145030934054</v>
       </c>
       <c r="S65">
-        <v>4.9397229224801213E-8</v>
+        <v>0.6460348340155504</v>
       </c>
       <c r="T65">
-        <v>4.9815186245353449E-8</v>
+        <v>0.65150102713276525</v>
       </c>
       <c r="U65">
-        <v>5.0236679660026782E-8</v>
+        <v>0.65701347049164138</v>
       </c>
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>0.75483585800191966</v>
+        <v>0.75679245283018914</v>
       </c>
       <c r="B66">
-        <v>4.11796210289431E-8</v>
+        <v>0.52399351246594905</v>
       </c>
       <c r="C66">
-        <v>4.1528047691386062E-8</v>
+        <v>0.52842709650893849</v>
       </c>
       <c r="D66">
-        <v>4.1879422441646932E-8</v>
+        <v>0.53289819374054304</v>
       </c>
       <c r="E66">
-        <v>4.22337702239183E-8</v>
+        <v>0.53740712156521619</v>
       </c>
       <c r="F66">
-        <v>4.2591116193449201E-8</v>
+        <v>0.54195420007301598</v>
       </c>
       <c r="G66">
-        <v>4.2951485718330782E-8</v>
+        <v>0.54653975206232797</v>
       </c>
       <c r="H66">
-        <v>4.3314904381297252E-8</v>
+        <v>0.5511641030627813</v>
       </c>
       <c r="I66">
-        <v>4.3681397981541981E-8</v>
+        <v>0.55582758135835753</v>
       </c>
       <c r="J66">
-        <v>4.4050992536549029E-8</v>
+        <v>0.56053051801069609</v>
       </c>
       <c r="K66">
-        <v>4.4423714283940091E-8</v>
+        <v>0.56527324688259661</v>
       </c>
       <c r="L66">
-        <v>4.4799589683337149E-8</v>
+        <v>0.57005610466171919</v>
       </c>
       <c r="M66">
-        <v>4.5178645418240782E-8</v>
+        <v>0.57487943088448656</v>
       </c>
       <c r="N66">
-        <v>4.5560908397924542E-8</v>
+        <v>0.57974356796018722</v>
       </c>
       <c r="O66">
-        <v>4.5946405759345139E-8</v>
+        <v>0.58464886119528447</v>
       </c>
       <c r="P66">
-        <v>4.6335164869069023E-8</v>
+        <v>0.58959565881792841</v>
       </c>
       <c r="Q66">
-        <v>4.6727213325215002E-8</v>
+        <v>0.59458431200267714</v>
       </c>
       <c r="R66">
-        <v>4.7122578959413569E-8</v>
+        <v>0.59961517489542748</v>
       </c>
       <c r="S66">
-        <v>4.7521289838782597E-8</v>
+        <v>0.60468860463855523</v>
       </c>
       <c r="T66">
-        <v>4.7923374267919862E-8</v>
+        <v>0.60980496139626827</v>
       </c>
       <c r="U66">
-        <v>4.8328860790912393E-8</v>
+        <v>0.6149646083801763</v>
       </c>
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>0.76689393899532232</v>
+        <v>0.76980607966456993</v>
       </c>
       <c r="B67">
-        <v>3.9554023886029069E-8</v>
+        <v>0.5045863453375804</v>
       </c>
       <c r="C67">
-        <v>3.9888696138576307E-8</v>
+        <v>0.50885572256416278</v>
       </c>
       <c r="D67">
-        <v>4.0226200100912372E-8</v>
+        <v>0.51316122360200433</v>
       </c>
       <c r="E67">
-        <v>4.0566559732538713E-8</v>
+        <v>0.51750315409983771</v>
       </c>
       <c r="F67">
-        <v>4.0909799195681577E-8</v>
+        <v>0.52188182229253366</v>
       </c>
       <c r="G67">
-        <v>4.125594285700728E-8</v>
+        <v>0.52629753902298237</v>
       </c>
       <c r="H67">
-        <v>4.1605015289351943E-8</v>
+        <v>0.53075061776415955</v>
       </c>
       <c r="I67">
-        <v>4.195704127346599E-8</v>
+        <v>0.53524137464138111</v>
       </c>
       <c r="J67">
-        <v>4.2312045799773313E-8</v>
+        <v>0.53977012845474426</v>
       </c>
       <c r="K67">
-        <v>4.2670054070145368E-8</v>
+        <v>0.5443372007017595</v>
       </c>
       <c r="L67">
-        <v>4.3031091499690242E-8</v>
+        <v>0.54894291560017394</v>
       </c>
       <c r="M67">
-        <v>4.3395183718556857E-8</v>
+        <v>0.55358760011098684</v>
       </c>
       <c r="N67">
-        <v>4.3762356573754548E-8</v>
+        <v>0.55827158396166165</v>
       </c>
       <c r="O67">
-        <v>4.4132636130987847E-8</v>
+        <v>0.56299519966953293</v>
       </c>
       <c r="P67">
-        <v>4.4506048676506961E-8</v>
+        <v>0.56775878256541235</v>
       </c>
       <c r="Q67">
-        <v>4.4882620718973778E-8</v>
+        <v>0.57256267081739265</v>
       </c>
       <c r="R67">
-        <v>4.5262378991343843E-8</v>
+        <v>0.57740720545485591</v>
       </c>
       <c r="S67">
-        <v>4.5645350452763987E-8</v>
+        <v>0.58229273039268259</v>
       </c>
       <c r="T67">
-        <v>4.6031562290486281E-8</v>
+        <v>0.58721959245566557</v>
       </c>
       <c r="U67">
-        <v>4.6421041921797997E-8</v>
+        <v>0.59218814140313258</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>0.78256944442521292</v>
+        <v>0.78281970649895227</v>
       </c>
       <c r="B68">
-        <v>3.7792960314538882E-8</v>
+        <v>0.48667203721908642</v>
       </c>
       <c r="C68">
-        <v>3.8112731956365752E-8</v>
+        <v>0.49078983892283162</v>
       </c>
       <c r="D68">
-        <v>3.8435209231783277E-8</v>
+        <v>0.49494248193566093</v>
       </c>
       <c r="E68">
-        <v>3.8760415033544173E-8</v>
+        <v>0.49913026105487301</v>
       </c>
       <c r="F68">
-        <v>3.9088372448100022E-8</v>
+        <v>0.50335347357208871</v>
       </c>
       <c r="G68">
-        <v>3.9419104757240173E-8</v>
+        <v>0.50761241929435574</v>
       </c>
       <c r="H68">
-        <v>3.9752635439744531E-8</v>
+        <v>0.51190740056543194</v>
       </c>
       <c r="I68">
-        <v>4.0088988173050339E-8</v>
+        <v>0.51623872228724932</v>
       </c>
       <c r="J68">
-        <v>4.0428186834932952E-8</v>
+        <v>0.52060669194155806</v>
       </c>
       <c r="K68">
-        <v>4.0770255505201068E-8</v>
+        <v>0.52501161961175624</v>
       </c>
       <c r="L68">
-        <v>4.1115218467406093E-8</v>
+        <v>0.52945381800490143</v>
       </c>
       <c r="M68">
-        <v>4.1463100210565963E-8</v>
+        <v>0.53393360247391042</v>
       </c>
       <c r="N68">
-        <v>4.1813925430903751E-8</v>
+        <v>0.53845129103994582</v>
       </c>
       <c r="O68">
-        <v>4.2167719033600788E-8</v>
+        <v>0.54300720441499339</v>
       </c>
       <c r="P68">
-        <v>4.252450613456473E-8</v>
+        <v>0.54760166602462845</v>
       </c>
       <c r="Q68">
-        <v>4.2884312062212468E-8</v>
+        <v>0.55223500203097631</v>
       </c>
       <c r="R68">
-        <v>4.3247162359268312E-8</v>
+        <v>0.55690754135586706</v>
       </c>
       <c r="S68">
-        <v>4.3613082784577173E-8</v>
+        <v>0.56161961570418495</v>
       </c>
       <c r="T68">
-        <v>4.398209931493324E-8</v>
+        <v>0.56637155958741703</v>
       </c>
       <c r="U68">
-        <v>4.4354238146924103E-8</v>
+        <v>0.57116371034739999</v>
       </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>0.79221590866606728</v>
+        <v>0.79883647798742197</v>
       </c>
       <c r="B69">
-        <v>3.6709228885929462E-8</v>
+        <v>0.46278629306109459</v>
       </c>
       <c r="C69">
-        <v>3.7019830921159191E-8</v>
+        <v>0.4667019940677235</v>
       </c>
       <c r="D69">
-        <v>3.7333061004626862E-8</v>
+        <v>0.47065082638053668</v>
       </c>
       <c r="E69">
-        <v>3.7648941372624378E-8</v>
+        <v>0.47463307032825369</v>
       </c>
       <c r="F69">
-        <v>3.7967494449588211E-8</v>
+        <v>0.47864900861149562</v>
       </c>
       <c r="G69">
-        <v>3.8288742849691112E-8</v>
+        <v>0.48269892632285383</v>
       </c>
       <c r="H69">
-        <v>3.8612709378447597E-8</v>
+        <v>0.48678311096712878</v>
       </c>
       <c r="I69">
-        <v>3.8939417034332938E-8</v>
+        <v>0.4909018524817404</v>
       </c>
       <c r="J69">
-        <v>3.9268889010415739E-8</v>
+        <v>0.4950554432573101</v>
       </c>
       <c r="K69">
-        <v>3.9601148696004517E-8</v>
+        <v>0.49924417815841871</v>
       </c>
       <c r="L69">
-        <v>3.9936219678308088E-8</v>
+        <v>0.50346835454453842</v>
       </c>
       <c r="M69">
-        <v>4.0274125744109958E-8</v>
+        <v>0.50772827229114204</v>
       </c>
       <c r="N69">
-        <v>4.0614890881457023E-8</v>
+        <v>0.51202423381099171</v>
       </c>
       <c r="O69">
-        <v>4.0958539281362532E-8</v>
+        <v>0.51635654407560738</v>
       </c>
       <c r="P69">
-        <v>4.1305095339523289E-8</v>
+        <v>0.52072551063691686</v>
       </c>
       <c r="Q69">
-        <v>4.1654583658051579E-8</v>
+        <v>0.52513144364908815</v>
       </c>
       <c r="R69">
-        <v>4.2007029047221749E-8</v>
+        <v>0.52957465589054864</v>
       </c>
       <c r="S69">
-        <v>4.2362456527231362E-8</v>
+        <v>0.53405546278618843</v>
       </c>
       <c r="T69">
-        <v>4.2720891329977438E-8</v>
+        <v>0.53857418242975275</v>
       </c>
       <c r="U69">
-        <v>4.3082358900847773E-8</v>
+        <v>0.54313113560642357</v>
       </c>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>0.80909722177989729</v>
+        <v>0.80984800838574411</v>
       </c>
       <c r="B70">
-        <v>3.5219098171591601E-8</v>
+        <v>0.45233627999197312</v>
       </c>
       <c r="C70">
-        <v>3.5517091997750263E-8</v>
+        <v>0.45616356194361352</v>
       </c>
       <c r="D70">
-        <v>3.5817607192286849E-8</v>
+        <v>0.46002322707516963</v>
       </c>
       <c r="E70">
-        <v>3.612066508885977E-8</v>
+        <v>0.46391554938535762</v>
       </c>
       <c r="F70">
-        <v>3.6426287201634572E-8</v>
+        <v>0.467840805191236</v>
       </c>
       <c r="G70">
-        <v>3.6734495226811242E-8</v>
+        <v>0.47179927314782161</v>
       </c>
       <c r="H70">
-        <v>3.7045311044164412E-8</v>
+        <v>0.47579123426787101</v>
       </c>
       <c r="I70">
-        <v>3.7358756718596612E-8</v>
+        <v>0.47981697194182998</v>
       </c>
       <c r="J70">
-        <v>3.7674854501704667E-8</v>
+        <v>0.48387677195795142</v>
       </c>
       <c r="K70">
-        <v>3.7993626833359363E-8</v>
+        <v>0.48797092252258339</v>
       </c>
       <c r="L70">
-        <v>3.8315096343298437E-8</v>
+        <v>0.49209971428062937</v>
       </c>
       <c r="M70">
-        <v>3.8639285852733043E-8</v>
+        <v>0.49626344033618058</v>
       </c>
       <c r="N70">
-        <v>3.8966218375967892E-8</v>
+        <v>0.50046239627332401</v>
       </c>
       <c r="O70">
-        <v>3.9295917122035008E-8</v>
+        <v>0.50469688017712588</v>
       </c>
       <c r="P70">
-        <v>3.9628405496341391E-8</v>
+        <v>0.50896719265479284</v>
       </c>
       <c r="Q70">
-        <v>3.996370710233047E-8</v>
+        <v>0.51327363685701188</v>
       </c>
       <c r="R70">
-        <v>4.0301845743157842E-8</v>
+        <v>0.51761651849947166</v>
       </c>
       <c r="S70">
-        <v>4.064284542338097E-8</v>
+        <v>0.52199614588456467</v>
       </c>
       <c r="T70">
-        <v>4.0986730350663337E-8</v>
+        <v>0.52641282992327432</v>
       </c>
       <c r="U70">
-        <v>4.1333524937492908E-8</v>
+        <v>0.53086688415724614</v>
       </c>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>0.82597853489372708</v>
+        <v>0.83187106918239007</v>
       </c>
       <c r="B71">
-        <v>3.4135366742982241E-8</v>
+        <v>0.43591483088335359</v>
       </c>
       <c r="C71">
-        <v>3.4424190962543762E-8</v>
+        <v>0.43960316860572662</v>
       </c>
       <c r="D71">
-        <v>3.4715458965130487E-8</v>
+        <v>0.44332271388102162</v>
       </c>
       <c r="E71">
-        <v>3.5009191427940048E-8</v>
+        <v>0.4470737307608067</v>
       </c>
       <c r="F71">
-        <v>3.5305409203122827E-8</v>
+        <v>0.45085648553082819</v>
       </c>
       <c r="G71">
-        <v>3.5604133319262241E-8</v>
+        <v>0.45467124672991388</v>
       </c>
       <c r="H71">
-        <v>3.5905384982867538E-8</v>
+        <v>0.45851828516903742</v>
       </c>
       <c r="I71">
-        <v>3.6209185579879278E-8</v>
+        <v>0.46239787395054249</v>
       </c>
       <c r="J71">
-        <v>3.6515556677187507E-8</v>
+        <v>0.46631028848753081</v>
       </c>
       <c r="K71">
-        <v>3.6824520024162878E-8</v>
+        <v>0.47025580652341381</v>
       </c>
       <c r="L71">
-        <v>3.7136097554200492E-8</v>
+        <v>0.47423470815162982</v>
       </c>
       <c r="M71">
-        <v>3.7450311386277091E-8</v>
+        <v>0.47824727583552729</v>
       </c>
       <c r="N71">
-        <v>3.7767183826521229E-8</v>
+        <v>0.48229379442841802</v>
       </c>
       <c r="O71">
-        <v>3.8086737369796811E-8</v>
+        <v>0.48637455119379802</v>
       </c>
       <c r="P71">
-        <v>3.840899470130001E-8</v>
+        <v>0.49048983582574113</v>
       </c>
       <c r="Q71">
-        <v>3.8733978698169647E-8</v>
+        <v>0.49463994046946369</v>
       </c>
       <c r="R71">
-        <v>3.9061712431111338E-8</v>
+        <v>0.49882515974206509</v>
       </c>
       <c r="S71">
-        <v>3.9392219166035233E-8</v>
+        <v>0.50304579075344202</v>
       </c>
       <c r="T71">
-        <v>3.9725522365707608E-8</v>
+        <v>0.50730213312737993</v>
       </c>
       <c r="U71">
-        <v>4.0061645691416657E-8</v>
+        <v>0.51159448902282478</v>
       </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>0.84527146476010551</v>
+        <v>0.84288259958071232</v>
       </c>
       <c r="B72">
-        <v>3.3187101742949063E-8</v>
+        <v>0.42994339484385591</v>
       </c>
       <c r="C72">
-        <v>3.3467902556738068E-8</v>
+        <v>0.43358120739194977</v>
       </c>
       <c r="D72">
-        <v>3.3751079266368659E-8</v>
+        <v>0.43724979999224067</v>
       </c>
       <c r="E72">
-        <v>3.4036651974635278E-8</v>
+        <v>0.44094943307915208</v>
       </c>
       <c r="F72">
-        <v>3.4324640954425048E-8</v>
+        <v>0.44468036929068011</v>
       </c>
       <c r="G72">
-        <v>3.4615066650156858E-8</v>
+        <v>0.44844287348703871</v>
       </c>
       <c r="H72">
-        <v>3.490794967923278E-8</v>
+        <v>0.45223721276946188</v>
       </c>
       <c r="I72">
-        <v>3.5203310833501623E-8</v>
+        <v>0.45606365649916553</v>
       </c>
       <c r="J72">
-        <v>3.5501171080735018E-8</v>
+        <v>0.45992247631646899</v>
       </c>
       <c r="K72">
-        <v>3.580155156611595E-8</v>
+        <v>0.46381394616007959</v>
       </c>
       <c r="L72">
-        <v>3.6104473613739803E-8</v>
+        <v>0.46773834228653932</v>
       </c>
       <c r="M72">
-        <v>3.6409958728128143E-8</v>
+        <v>0.47169594328983538</v>
       </c>
       <c r="N72">
-        <v>3.671802859575541E-8</v>
+        <v>0.47568703012117958</v>
       </c>
       <c r="O72">
-        <v>3.7028705086588402E-8</v>
+        <v>0.47971188610895171</v>
       </c>
       <c r="P72">
-        <v>3.7342010255638813E-8</v>
+        <v>0.48377079697881342</v>
       </c>
       <c r="Q72">
-        <v>3.7657966344528939E-8</v>
+        <v>0.48786405087399182</v>
       </c>
       <c r="R72">
-        <v>3.7976595783070667E-8</v>
+        <v>0.49199193837573568</v>
       </c>
       <c r="S72">
-        <v>3.8297921190857713E-8</v>
+        <v>0.49615475252394309</v>
       </c>
       <c r="T72">
-        <v>3.8621965378871351E-8</v>
+        <v>0.50035278883796408</v>
       </c>
       <c r="U72">
-        <v>3.8948751351099938E-8</v>
+        <v>0.50458634533758095</v>
       </c>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>0.86215277787393552</v>
+        <v>0.86090146750524044</v>
       </c>
       <c r="B73">
-        <v>3.2645236028644432E-8</v>
+        <v>0.42098624078460889</v>
       </c>
       <c r="C73">
-        <v>3.292145203913488E-8</v>
+        <v>0.42454826557128422</v>
       </c>
       <c r="D73">
-        <v>3.3200005152790527E-8</v>
+        <v>0.42814042915906908</v>
       </c>
       <c r="E73">
-        <v>3.348091514417548E-8</v>
+        <v>0.43176298655666978</v>
       </c>
       <c r="F73">
-        <v>3.3764201955169241E-8</v>
+        <v>0.43541619493045758</v>
       </c>
       <c r="G73">
-        <v>3.4049885696382417E-8</v>
+        <v>0.43910031362272528</v>
       </c>
       <c r="H73">
-        <v>3.4337986648584399E-8</v>
+        <v>0.44281560417009808</v>
       </c>
       <c r="I73">
-        <v>3.4628525264143012E-8</v>
+        <v>0.44656233032209952</v>
       </c>
       <c r="J73">
-        <v>3.4921522168476488E-8</v>
+        <v>0.45034075805987578</v>
       </c>
       <c r="K73">
-        <v>3.5216998161517758E-8</v>
+        <v>0.45415115561507802</v>
       </c>
       <c r="L73">
-        <v>3.5514974219190887E-8</v>
+        <v>0.45799379348890301</v>
       </c>
       <c r="M73">
-        <v>3.581547149490023E-8</v>
+        <v>0.46186894447129723</v>
       </c>
       <c r="N73">
-        <v>3.6118511321032138E-8</v>
+        <v>0.46577688366032172</v>
       </c>
       <c r="O73">
-        <v>3.6424115210469353E-8</v>
+        <v>0.46971788848168189</v>
       </c>
       <c r="P73">
-        <v>3.6732304858118179E-8</v>
+        <v>0.47369223870842148</v>
       </c>
       <c r="Q73">
-        <v>3.704310214244859E-8</v>
+        <v>0.4777002164807837</v>
       </c>
       <c r="R73">
-        <v>3.7356529127047478E-8</v>
+        <v>0.48174210632624132</v>
       </c>
       <c r="S73">
-        <v>3.7672608062184887E-8</v>
+        <v>0.48581819517969432</v>
       </c>
       <c r="T73">
-        <v>3.7991361386393552E-8</v>
+        <v>0.48992877240383981</v>
       </c>
       <c r="U73">
-        <v>3.8312811728061872E-8</v>
+        <v>0.49407412980971471</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>0.87421085886733818</v>
+        <v>0.8779192872117404</v>
       </c>
       <c r="B74">
-        <v>3.2374303171492047E-8</v>
+        <v>0.41800052276485972</v>
       </c>
       <c r="C74">
-        <v>3.2648226780333207E-8</v>
+        <v>0.42153728496439541</v>
       </c>
       <c r="D74">
-        <v>3.2924468096001392E-8</v>
+        <v>0.42510397221467833</v>
       </c>
       <c r="E74">
-        <v>3.3203046728945488E-8</v>
+        <v>0.42870083771584211</v>
       </c>
       <c r="F74">
-        <v>3.3483982455541252E-8</v>
+        <v>0.43232813681038318</v>
       </c>
       <c r="G74">
-        <v>3.3767295219495127E-8</v>
+        <v>0.4359861270012873</v>
       </c>
       <c r="H74">
-        <v>3.4053005133260132E-8</v>
+        <v>0.43967506797030992</v>
       </c>
       <c r="I74">
-        <v>3.4341132479463607E-8</v>
+        <v>0.44339522159641059</v>
       </c>
       <c r="J74">
-        <v>3.463169771234716E-8</v>
+        <v>0.44714685197434462</v>
       </c>
       <c r="K74">
-        <v>3.4924721459218592E-8</v>
+        <v>0.45093022543341038</v>
       </c>
       <c r="L74">
-        <v>3.522022452191635E-8</v>
+        <v>0.45474561055635732</v>
       </c>
       <c r="M74">
-        <v>3.551822787828619E-8</v>
+        <v>0.45859327819845092</v>
       </c>
       <c r="N74">
-        <v>3.5818752683670433E-8</v>
+        <v>0.46247350150670208</v>
       </c>
       <c r="O74">
-        <v>3.6121820272409753E-8</v>
+        <v>0.46638655593925832</v>
       </c>
       <c r="P74">
-        <v>3.6427452159357772E-8</v>
+        <v>0.47033271928495718</v>
       </c>
       <c r="Q74">
-        <v>3.673567004140833E-8</v>
+        <v>0.47431227168304729</v>
       </c>
       <c r="R74">
-        <v>3.7046495799035807E-8</v>
+        <v>0.47832549564307619</v>
       </c>
       <c r="S74">
-        <v>3.7359951497848398E-8</v>
+        <v>0.48237267606494438</v>
       </c>
       <c r="T74">
-        <v>3.7676059390154567E-8</v>
+        <v>0.48645410025913149</v>
       </c>
       <c r="U74">
-        <v>3.7994841916542737E-8</v>
+        <v>0.49057005796709219</v>
       </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>0.89470959641765591</v>
+        <v>0.89293501048217994</v>
       </c>
       <c r="B75">
-        <v>3.2374303171492047E-8</v>
+        <v>0.41949338177473439</v>
       </c>
       <c r="C75">
-        <v>3.2648226780333207E-8</v>
+        <v>0.42304277526783979</v>
       </c>
       <c r="D75">
-        <v>3.2924468096001392E-8</v>
+        <v>0.42662220068687368</v>
       </c>
       <c r="E75">
-        <v>3.3203046728945488E-8</v>
+        <v>0.43023191213625589</v>
       </c>
       <c r="F75">
-        <v>3.3483982455541252E-8</v>
+        <v>0.43387216587042038</v>
       </c>
       <c r="G75">
-        <v>3.3767295219495127E-8</v>
+        <v>0.43754322031200638</v>
       </c>
       <c r="H75">
-        <v>3.4053005133260132E-8</v>
+        <v>0.44124533607020411</v>
       </c>
       <c r="I75">
-        <v>3.4341132479463607E-8</v>
+        <v>0.44497877595925511</v>
       </c>
       <c r="J75">
-        <v>3.463169771234716E-8</v>
+        <v>0.44874380501711031</v>
       </c>
       <c r="K75">
-        <v>3.4924721459218592E-8</v>
+        <v>0.45254069052424423</v>
       </c>
       <c r="L75">
-        <v>3.522022452191635E-8</v>
+        <v>0.45636970202263022</v>
       </c>
       <c r="M75">
-        <v>3.551822787828619E-8</v>
+        <v>0.46023111133487399</v>
       </c>
       <c r="N75">
-        <v>3.5818752683670433E-8</v>
+        <v>0.46412519258351198</v>
       </c>
       <c r="O75">
-        <v>3.6121820272409753E-8</v>
+        <v>0.4680522222104701</v>
       </c>
       <c r="P75">
-        <v>3.6427452159357772E-8</v>
+        <v>0.47201247899668941</v>
       </c>
       <c r="Q75">
-        <v>3.673567004140833E-8</v>
+        <v>0.47600624408191561</v>
       </c>
       <c r="R75">
-        <v>3.7046495799035807E-8</v>
+        <v>0.48003380098465881</v>
       </c>
       <c r="S75">
-        <v>3.7359951497848398E-8</v>
+        <v>0.48409543562231938</v>
       </c>
       <c r="T75">
-        <v>3.7676059390154567E-8</v>
+        <v>0.48819143633148571</v>
       </c>
       <c r="U75">
-        <v>3.7994841916542737E-8</v>
+        <v>0.49232209388840348</v>
       </c>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>0.91159090953148592</v>
+        <v>0.91195492662473832</v>
       </c>
       <c r="B76">
-        <v>3.2374303171492047E-8</v>
+        <v>0.41949338177473439</v>
       </c>
       <c r="C76">
-        <v>3.2648226780333207E-8</v>
+        <v>0.42304277526783979</v>
       </c>
       <c r="D76">
-        <v>3.2924468096001392E-8</v>
+        <v>0.42662220068687368</v>
       </c>
       <c r="E76">
-        <v>3.3203046728945488E-8</v>
+        <v>0.43023191213625589</v>
       </c>
       <c r="F76">
-        <v>3.3483982455541252E-8</v>
+        <v>0.43387216587042038</v>
       </c>
       <c r="G76">
-        <v>3.3767295219495127E-8</v>
+        <v>0.43754322031200638</v>
       </c>
       <c r="H76">
-        <v>3.4053005133260132E-8</v>
+        <v>0.44124533607020411</v>
       </c>
       <c r="I76">
-        <v>3.4341132479463607E-8</v>
+        <v>0.44497877595925511</v>
       </c>
       <c r="J76">
-        <v>3.463169771234716E-8</v>
+        <v>0.44874380501711031</v>
       </c>
       <c r="K76">
-        <v>3.4924721459218592E-8</v>
+        <v>0.45254069052424423</v>
       </c>
       <c r="L76">
-        <v>3.522022452191635E-8</v>
+        <v>0.45636970202263022</v>
       </c>
       <c r="M76">
-        <v>3.551822787828619E-8</v>
+        <v>0.46023111133487399</v>
       </c>
       <c r="N76">
-        <v>3.5818752683670433E-8</v>
+        <v>0.46412519258351198</v>
       </c>
       <c r="O76">
-        <v>3.6121820272409753E-8</v>
+        <v>0.4680522222104701</v>
       </c>
       <c r="P76">
-        <v>3.6427452159357772E-8</v>
+        <v>0.47201247899668941</v>
       </c>
       <c r="Q76">
-        <v>3.673567004140833E-8</v>
+        <v>0.47600624408191561</v>
       </c>
       <c r="R76">
-        <v>3.7046495799035807E-8</v>
+        <v>0.48003380098465881</v>
       </c>
       <c r="S76">
-        <v>3.7359951497848398E-8</v>
+        <v>0.48409543562231938</v>
       </c>
       <c r="T76">
-        <v>3.7676059390154567E-8</v>
+        <v>0.48819143633148571</v>
       </c>
       <c r="U76">
-        <v>3.7994841916542737E-8</v>
+        <v>0.49232209388840348</v>
       </c>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>0.92967803032925511</v>
+        <v>0.93397798742138427</v>
       </c>
       <c r="B77">
-        <v>3.2238836742915931E-8</v>
+        <v>0.41949338177473439</v>
       </c>
       <c r="C77">
-        <v>3.2511614150932453E-8</v>
+        <v>0.42304277526783979</v>
       </c>
       <c r="D77">
-        <v>3.2786699567606897E-8</v>
+        <v>0.42662220068687368</v>
       </c>
       <c r="E77">
-        <v>3.3064112521330588E-8</v>
+        <v>0.43023191213625589</v>
       </c>
       <c r="F77">
-        <v>3.3343872705727347E-8</v>
+        <v>0.43387216587042038</v>
       </c>
       <c r="G77">
-        <v>3.3625999981051548E-8</v>
+        <v>0.43754322031200638</v>
       </c>
       <c r="H77">
-        <v>3.3910514375598082E-8</v>
+        <v>0.44124533607020411</v>
       </c>
       <c r="I77">
-        <v>3.4197436087124007E-8</v>
+        <v>0.44497877595925511</v>
       </c>
       <c r="J77">
-        <v>3.4486785484282568E-8</v>
+        <v>0.44874380501711031</v>
       </c>
       <c r="K77">
-        <v>3.4778583108069088E-8</v>
+        <v>0.45254069052424423</v>
       </c>
       <c r="L77">
-        <v>3.5072849673279167E-8</v>
+        <v>0.45636970202263022</v>
       </c>
       <c r="M77">
-        <v>3.536960606997926E-8</v>
+        <v>0.46023111133487399</v>
       </c>
       <c r="N77">
-        <v>3.5668873364989663E-8</v>
+        <v>0.46412519258351198</v>
       </c>
       <c r="O77">
-        <v>3.5970672803380039E-8</v>
+        <v>0.4680522222104701</v>
       </c>
       <c r="P77">
-        <v>3.6275025809977668E-8</v>
+        <v>0.47201247899668941</v>
       </c>
       <c r="Q77">
-        <v>3.6581953990888289E-8</v>
+        <v>0.47600624408191561</v>
       </c>
       <c r="R77">
-        <v>3.6891479135030061E-8</v>
+        <v>0.48003380098465881</v>
       </c>
       <c r="S77">
-        <v>3.7203623215680253E-8</v>
+        <v>0.48409543562231938</v>
       </c>
       <c r="T77">
-        <v>3.7518408392035167E-8</v>
+        <v>0.48819143633148571</v>
       </c>
       <c r="U77">
-        <v>3.7835857010783278E-8</v>
+        <v>0.49232209388840348</v>
       </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>0.95499999999999985</v>
+        <v>0.95499999999999996</v>
       </c>
       <c r="B78">
-        <v>3.2645236028644432E-8</v>
+        <v>0.42247909979448278</v>
       </c>
       <c r="C78">
-        <v>3.292145203913488E-8</v>
+        <v>0.42605375587472788</v>
       </c>
       <c r="D78">
-        <v>3.3200005152790527E-8</v>
+        <v>0.42965865763126382</v>
       </c>
       <c r="E78">
-        <v>3.348091514417548E-8</v>
+        <v>0.43329406097708278</v>
       </c>
       <c r="F78">
-        <v>3.3764201955169241E-8</v>
+        <v>0.43696022399049411</v>
       </c>
       <c r="G78">
-        <v>3.4049885696382417E-8</v>
+        <v>0.44065740693344357</v>
       </c>
       <c r="H78">
-        <v>3.4337986648584399E-8</v>
+        <v>0.44438587226999138</v>
       </c>
       <c r="I78">
-        <v>3.4628525264143012E-8</v>
+        <v>0.44814588468494321</v>
       </c>
       <c r="J78">
-        <v>3.4921522168476488E-8</v>
+        <v>0.45193771110264069</v>
       </c>
       <c r="K78">
-        <v>3.5216998161517758E-8</v>
+        <v>0.45576162070591092</v>
       </c>
       <c r="L78">
-        <v>3.5514974219190887E-8</v>
+        <v>0.45961788495517503</v>
       </c>
       <c r="M78">
-        <v>3.581547149490023E-8</v>
+        <v>0.46350677760771958</v>
       </c>
       <c r="N78">
-        <v>3.6118511321032138E-8</v>
+        <v>0.46742857473713068</v>
       </c>
       <c r="O78">
-        <v>3.6424115210469353E-8</v>
+        <v>0.47138355475289279</v>
       </c>
       <c r="P78">
-        <v>3.6732304858118179E-8</v>
+        <v>0.47537199842015282</v>
       </c>
       <c r="Q78">
-        <v>3.704310214244859E-8</v>
+        <v>0.47939418887965102</v>
       </c>
       <c r="R78">
-        <v>3.7356529127047478E-8</v>
+        <v>0.48345041166782299</v>
       </c>
       <c r="S78">
-        <v>3.7672608062184887E-8</v>
+        <v>0.48754095473706838</v>
       </c>
       <c r="T78">
-        <v>3.7991361386393552E-8</v>
+        <v>0.49166610847619319</v>
       </c>
       <c r="U78">
-        <v>3.8312811728061872E-8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:B78"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>5.6159999999999998E-5</v>
-      </c>
-      <c r="B2">
-        <v>9.3600000000000107E-5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>5.6639999999999898E-5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>5.6639999999999898E-5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>5.6639999999999898E-5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5.63999999999999E-5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>5.5679999999999901E-5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>5.4959999999999901E-5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>5.3999999999999998E-5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>5.2799999999999901E-5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>5.1839999999999998E-5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>5.1119999999999998E-5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>5.0879999999999899E-5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>5.0879999999999899E-5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>5.1359999999999901E-5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>5.2799999999999901E-5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>5.3999999999999998E-5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>5.5439999999999998E-5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>5.7599999999999997E-5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>5.99999999999999E-5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>6.2639999999999997E-5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>6.6959999999999996E-5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>7.1039999999999997E-5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>7.3679999999999999E-5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>7.6799999999999997E-5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>8.1359999999999994E-5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>8.5439999999999995E-5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>8.9759999999999994E-5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>9.3599999999999998E-5</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>9.8879999999999894E-5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>1.04159999999999E-4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>1.07759999999999E-4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>1.12799999999999E-4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>1.18559999999999E-4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>1.2239999999999999E-4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>1.2695999999999999E-4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>1.3031999999999901E-4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>1.3319999999999901E-4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>1.3607999999999901E-4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>1.3799999999999999E-4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>1.404E-4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>1.42799999999999E-4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>1.4375999999999999E-4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>1.4448E-4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>1.4423999999999999E-4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>1.4255999999999999E-4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>1.4063999999999901E-4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48">
-        <v>1.3847999999999999E-4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>1.35359999999999E-4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>1.3319999999999901E-4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>1.2935999999999999E-4</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>1.2575999999999999E-4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>1.2215999999999901E-4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>1.1783999999999899E-4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>1.14239999999999E-4</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>1.10399999999999E-4</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>1.0656E-4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>1.02959999999999E-4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>1.00079999999999E-4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>9.5279999999999996E-5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>9.1919999999999906E-5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>8.8799999999999895E-5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>8.3279999999999894E-5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>7.8479999999999994E-5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>7.4159999999999995E-5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>7.1279999999999995E-5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>6.8399999999999996E-5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>6.5279999999999998E-5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>6.3359999999999895E-5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>6.07199999999999E-5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>5.8799999999999898E-5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>5.71199999999999E-5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>5.6159999999999998E-5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>5.5679999999999901E-5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>5.5679999999999901E-5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>5.5679999999999901E-5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>5.5439999999999998E-5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>5.6159999999999998E-5</v>
+        <v>0.495826165731025</v>
       </c>
     </row>
   </sheetData>
